--- a/public/import_template/v0.2node/node_module.xlsx
+++ b/public/import_template/v0.2node/node_module.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\ddit\code\umi_max.250519_master\public\import_template\v0.2node\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\ddit\code\umi_max.260226_github\public\import_template\v0.2node\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC75E4B-3BA5-4B3B-BD9E-4CC0ABCEB439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0908BCD0-0D6F-41A6-AC17-9C2653A62522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="762" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="762" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表" sheetId="8" r:id="rId1"/>
@@ -2852,7 +2852,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2945,12 +2945,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2958,24 +2952,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6C3FF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3092,7 +3068,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3190,20 +3166,12 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3213,70 +3181,14 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3295,6 +3207,19 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -6257,10 +6182,10 @@
       <c r="G173" s="26"/>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A174" s="51" t="s">
+      <c r="A174" s="26" t="s">
         <v>629</v>
       </c>
-      <c r="B174" s="60" t="s">
+      <c r="B174" s="42" t="s">
         <v>652</v>
       </c>
       <c r="C174" s="26" t="s">
@@ -6272,18 +6197,18 @@
       <c r="G174" s="26"/>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A175" s="51" t="s">
+      <c r="A175" s="26" t="s">
         <v>662</v>
       </c>
-      <c r="B175" s="60" t="s">
+      <c r="B175" s="42" t="s">
         <v>678</v>
       </c>
       <c r="C175" s="26" t="s">
         <v>679</v>
       </c>
-      <c r="D175" s="61"/>
-      <c r="E175" s="61"/>
-      <c r="F175" s="61"/>
+      <c r="D175" s="43"/>
+      <c r="E175" s="43"/>
+      <c r="F175" s="43"/>
       <c r="G175" s="26"/>
     </row>
     <row r="176" spans="1:7" s="25" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
@@ -6362,7 +6287,7 @@
       <c r="G180" s="26"/>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A181" s="38" t="s">
+      <c r="A181" s="37" t="s">
         <v>500</v>
       </c>
       <c r="B181" s="26" t="s">
@@ -6688,13 +6613,13 @@
       <c r="G202" s="24"/>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A203" s="62" t="s">
+      <c r="A203" s="26" t="s">
         <v>682</v>
       </c>
-      <c r="B203" s="62" t="s">
+      <c r="B203" s="26" t="s">
         <v>685</v>
       </c>
-      <c r="C203" s="62" t="s">
+      <c r="C203" s="26" t="s">
         <v>36</v>
       </c>
       <c r="D203" s="26" t="s">
@@ -6707,13 +6632,13 @@
       <c r="G203" s="26"/>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A204" s="62" t="s">
+      <c r="A204" s="26" t="s">
         <v>683</v>
       </c>
-      <c r="B204" s="62" t="s">
+      <c r="B204" s="26" t="s">
         <v>686</v>
       </c>
-      <c r="C204" s="62" t="s">
+      <c r="C204" s="26" t="s">
         <v>457</v>
       </c>
       <c r="D204" s="26"/>
@@ -6722,16 +6647,16 @@
       <c r="G204" s="26"/>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A205" s="62" t="s">
+      <c r="A205" s="26" t="s">
         <v>684</v>
       </c>
-      <c r="B205" s="62" t="s">
+      <c r="B205" s="26" t="s">
         <v>687</v>
       </c>
-      <c r="C205" s="62" t="s">
+      <c r="C205" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="D205" s="27"/>
+      <c r="D205" s="52"/>
       <c r="E205" s="27"/>
       <c r="F205" s="27"/>
       <c r="G205" s="26"/>
@@ -6748,51 +6673,51 @@
       <c r="G206" s="24"/>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A207" s="62" t="s">
+      <c r="A207" s="26" t="s">
         <v>479</v>
       </c>
-      <c r="B207" s="62" t="s">
+      <c r="B207" s="26" t="s">
         <v>454</v>
       </c>
-      <c r="C207" s="62" t="s">
+      <c r="C207" s="26" t="s">
         <v>455</v>
       </c>
       <c r="D207" s="26" t="s">
         <v>235</v>
       </c>
-      <c r="E207" s="27"/>
+      <c r="E207" s="52"/>
       <c r="F207" s="26" t="s">
         <v>236</v>
       </c>
       <c r="G207" s="26"/>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A208" s="62" t="s">
+      <c r="A208" s="26" t="s">
         <v>488</v>
       </c>
-      <c r="B208" s="62" t="s">
+      <c r="B208" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="C208" s="62" t="s">
+      <c r="C208" s="26" t="s">
         <v>455</v>
       </c>
       <c r="D208" s="26"/>
-      <c r="E208" s="27"/>
+      <c r="E208" s="52"/>
       <c r="F208" s="26"/>
       <c r="G208" s="26"/>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A209" s="62" t="s">
+      <c r="A209" s="26" t="s">
         <v>682</v>
       </c>
-      <c r="B209" s="62" t="s">
+      <c r="B209" s="26" t="s">
         <v>685</v>
       </c>
-      <c r="C209" s="62" t="s">
+      <c r="C209" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="D209" s="27"/>
-      <c r="E209" s="27"/>
+      <c r="D209" s="52"/>
+      <c r="E209" s="52"/>
       <c r="F209" s="27"/>
       <c r="G209" s="26"/>
     </row>
@@ -6919,7 +6844,7 @@
       <c r="AD1" s="19" t="s">
         <v>729</v>
       </c>
-      <c r="AE1" s="66" t="s">
+      <c r="AE1" s="44" t="s">
         <v>708</v>
       </c>
     </row>
@@ -7657,110 +7582,110 @@
       <c r="AE12" s="3"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="2" t="s">
         <v>737</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="C13" s="39">
-        <v>1</v>
-      </c>
-      <c r="D13" s="39">
-        <v>1</v>
-      </c>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="L13" s="39"/>
-      <c r="M13" s="39"/>
-      <c r="N13" s="39">
-        <v>1</v>
-      </c>
-      <c r="O13" s="39">
-        <v>1</v>
-      </c>
-      <c r="P13" s="39">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="39">
-        <v>1</v>
-      </c>
-      <c r="R13" s="39">
-        <v>1</v>
-      </c>
-      <c r="S13" s="39"/>
-      <c r="T13" s="39"/>
-      <c r="U13" s="42" t="s">
+      <c r="C13" s="7">
+        <v>1</v>
+      </c>
+      <c r="D13" s="7">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7">
+        <v>1</v>
+      </c>
+      <c r="O13" s="7">
+        <v>1</v>
+      </c>
+      <c r="P13" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>1</v>
+      </c>
+      <c r="R13" s="7">
+        <v>1</v>
+      </c>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7" t="s">
         <v>732</v>
       </c>
-      <c r="V13" s="39"/>
-      <c r="W13" s="39"/>
-      <c r="X13" s="39"/>
-      <c r="Y13" s="39"/>
-      <c r="Z13" s="40"/>
-      <c r="AA13" s="40"/>
-      <c r="AB13" s="40"/>
-      <c r="AC13" s="39"/>
-      <c r="AD13" s="39"/>
-      <c r="AE13" s="3"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7"/>
+      <c r="Z13" s="2"/>
+      <c r="AA13" s="2"/>
+      <c r="AB13" s="2"/>
+      <c r="AC13" s="7"/>
+      <c r="AD13" s="7"/>
+      <c r="AE13" s="7"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A14" s="40" t="s">
+      <c r="A14" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="C14" s="39">
-        <v>1</v>
-      </c>
-      <c r="D14" s="39">
-        <v>1</v>
-      </c>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
-      <c r="L14" s="39"/>
-      <c r="M14" s="39"/>
-      <c r="N14" s="39">
-        <v>1</v>
-      </c>
-      <c r="O14" s="39">
-        <v>1</v>
-      </c>
-      <c r="P14" s="39">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="39">
-        <v>1</v>
-      </c>
-      <c r="R14" s="39">
-        <v>1</v>
-      </c>
-      <c r="S14" s="39"/>
-      <c r="T14" s="39"/>
-      <c r="U14" s="42" t="s">
+      <c r="C14" s="7">
+        <v>1</v>
+      </c>
+      <c r="D14" s="7">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7">
+        <v>1</v>
+      </c>
+      <c r="O14" s="7">
+        <v>1</v>
+      </c>
+      <c r="P14" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="7">
+        <v>1</v>
+      </c>
+      <c r="R14" s="7">
+        <v>1</v>
+      </c>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7" t="s">
         <v>733</v>
       </c>
-      <c r="V14" s="39"/>
-      <c r="W14" s="39"/>
-      <c r="X14" s="39"/>
-      <c r="Y14" s="39"/>
-      <c r="Z14" s="40"/>
-      <c r="AA14" s="40"/>
-      <c r="AB14" s="40"/>
-      <c r="AC14" s="39"/>
-      <c r="AD14" s="39"/>
-      <c r="AE14" s="3"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="2"/>
+      <c r="AA14" s="2"/>
+      <c r="AB14" s="2"/>
+      <c r="AC14" s="7"/>
+      <c r="AD14" s="7"/>
+      <c r="AE14" s="7"/>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
@@ -8140,50 +8065,50 @@
       <c r="AJ1" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="66" t="s">
+      <c r="AK1" s="44" t="s">
         <v>708</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="45" t="s">
         <v>533</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="70"/>
-      <c r="O2" s="70"/>
-      <c r="P2" s="70"/>
-      <c r="Q2" s="70"/>
-      <c r="R2" s="70"/>
-      <c r="S2" s="70"/>
-      <c r="T2" s="70"/>
-      <c r="U2" s="70"/>
-      <c r="V2" s="70"/>
-      <c r="W2" s="70"/>
-      <c r="X2" s="70"/>
-      <c r="Y2" s="70"/>
-      <c r="Z2" s="70"/>
-      <c r="AA2" s="70"/>
-      <c r="AB2" s="70"/>
-      <c r="AC2" s="70"/>
-      <c r="AD2" s="70"/>
-      <c r="AE2" s="70"/>
-      <c r="AF2" s="70"/>
-      <c r="AG2" s="70"/>
-      <c r="AH2" s="70"/>
-      <c r="AI2" s="70"/>
-      <c r="AJ2" s="70"/>
-      <c r="AK2" s="71"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="46"/>
+      <c r="Q2" s="46"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="46"/>
+      <c r="T2" s="46"/>
+      <c r="U2" s="46"/>
+      <c r="V2" s="46"/>
+      <c r="W2" s="46"/>
+      <c r="X2" s="46"/>
+      <c r="Y2" s="46"/>
+      <c r="Z2" s="46"/>
+      <c r="AA2" s="46"/>
+      <c r="AB2" s="46"/>
+      <c r="AC2" s="46"/>
+      <c r="AD2" s="46"/>
+      <c r="AE2" s="46"/>
+      <c r="AF2" s="46"/>
+      <c r="AG2" s="46"/>
+      <c r="AH2" s="46"/>
+      <c r="AI2" s="46"/>
+      <c r="AJ2" s="46"/>
+      <c r="AK2" s="47"/>
     </row>
     <row r="3" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -8405,7 +8330,7 @@
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
-      <c r="M6" s="37" t="s">
+      <c r="M6" s="2" t="s">
         <v>620</v>
       </c>
       <c r="N6" s="2" t="s">
@@ -8466,7 +8391,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
-      <c r="M7" s="37" t="s">
+      <c r="M7" s="2" t="s">
         <v>619</v>
       </c>
       <c r="N7" s="2"/>
@@ -8775,7 +8700,7 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
-      <c r="M12" s="64" t="s">
+      <c r="M12" s="52" t="s">
         <v>709</v>
       </c>
       <c r="N12" s="2"/>
@@ -8803,7 +8728,7 @@
       <c r="Z12" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AA12" s="64" t="s">
+      <c r="AA12" s="52" t="s">
         <v>709</v>
       </c>
       <c r="AB12" s="2"/>
@@ -9042,7 +8967,7 @@
         <v>42</v>
       </c>
       <c r="AA16" s="2"/>
-      <c r="AB16" s="1">
+      <c r="AB16" s="2">
         <v>1</v>
       </c>
       <c r="AC16" s="2"/>
@@ -9185,7 +9110,7 @@
         <v>85</v>
       </c>
       <c r="AB18" s="2"/>
-      <c r="AC18" s="27"/>
+      <c r="AC18" s="52"/>
       <c r="AD18" s="2"/>
       <c r="AE18" s="2"/>
       <c r="AF18" s="2"/>
@@ -9229,7 +9154,7 @@
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
-      <c r="P19" s="65" t="s">
+      <c r="P19" s="54" t="s">
         <v>710</v>
       </c>
       <c r="Q19" s="2"/>
@@ -9298,7 +9223,7 @@
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
-      <c r="P20" s="65" t="s">
+      <c r="P20" s="54" t="s">
         <v>711</v>
       </c>
       <c r="Q20" s="2"/>
@@ -9386,7 +9311,7 @@
         <v>80</v>
       </c>
       <c r="AB21" s="2"/>
-      <c r="AC21" s="63" t="s">
+      <c r="AC21" s="52" t="s">
         <v>714</v>
       </c>
       <c r="AD21" s="2"/>
@@ -9443,9 +9368,9 @@
       <c r="Z22" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="AA22" s="1"/>
-      <c r="AB22" s="1"/>
-      <c r="AC22" s="1"/>
+      <c r="AA22" s="2"/>
+      <c r="AB22" s="2"/>
+      <c r="AC22" s="2"/>
       <c r="AD22" s="1">
         <v>100</v>
       </c>
@@ -9496,9 +9421,9 @@
       <c r="Z23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AA23" s="1"/>
-      <c r="AB23" s="1"/>
-      <c r="AC23" s="1"/>
+      <c r="AA23" s="2"/>
+      <c r="AB23" s="2"/>
+      <c r="AC23" s="2"/>
       <c r="AD23" s="1"/>
       <c r="AE23" s="1"/>
       <c r="AF23" s="1"/>
@@ -11433,45 +11358,45 @@
       <c r="AK59" s="1"/>
     </row>
     <row r="60" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="69" t="s">
+      <c r="A60" s="45" t="s">
         <v>532</v>
       </c>
-      <c r="B60" s="70"/>
-      <c r="C60" s="70"/>
-      <c r="D60" s="70"/>
-      <c r="E60" s="70"/>
-      <c r="F60" s="70"/>
-      <c r="G60" s="70"/>
-      <c r="H60" s="70"/>
-      <c r="I60" s="70"/>
-      <c r="J60" s="70"/>
-      <c r="K60" s="70"/>
-      <c r="L60" s="70"/>
-      <c r="M60" s="70"/>
-      <c r="N60" s="70"/>
-      <c r="O60" s="70"/>
-      <c r="P60" s="70"/>
-      <c r="Q60" s="70"/>
-      <c r="R60" s="70"/>
-      <c r="S60" s="70"/>
-      <c r="T60" s="70"/>
-      <c r="U60" s="70"/>
-      <c r="V60" s="70"/>
-      <c r="W60" s="70"/>
-      <c r="X60" s="70"/>
-      <c r="Y60" s="70"/>
-      <c r="Z60" s="70"/>
-      <c r="AA60" s="70"/>
-      <c r="AB60" s="70"/>
-      <c r="AC60" s="70"/>
-      <c r="AD60" s="70"/>
-      <c r="AE60" s="70"/>
-      <c r="AF60" s="70"/>
-      <c r="AG60" s="70"/>
-      <c r="AH60" s="70"/>
-      <c r="AI60" s="70"/>
-      <c r="AJ60" s="70"/>
-      <c r="AK60" s="71"/>
+      <c r="B60" s="46"/>
+      <c r="C60" s="46"/>
+      <c r="D60" s="46"/>
+      <c r="E60" s="46"/>
+      <c r="F60" s="46"/>
+      <c r="G60" s="46"/>
+      <c r="H60" s="46"/>
+      <c r="I60" s="46"/>
+      <c r="J60" s="46"/>
+      <c r="K60" s="46"/>
+      <c r="L60" s="46"/>
+      <c r="M60" s="46"/>
+      <c r="N60" s="46"/>
+      <c r="O60" s="46"/>
+      <c r="P60" s="46"/>
+      <c r="Q60" s="46"/>
+      <c r="R60" s="46"/>
+      <c r="S60" s="46"/>
+      <c r="T60" s="46"/>
+      <c r="U60" s="46"/>
+      <c r="V60" s="46"/>
+      <c r="W60" s="46"/>
+      <c r="X60" s="46"/>
+      <c r="Y60" s="46"/>
+      <c r="Z60" s="46"/>
+      <c r="AA60" s="46"/>
+      <c r="AB60" s="46"/>
+      <c r="AC60" s="46"/>
+      <c r="AD60" s="46"/>
+      <c r="AE60" s="46"/>
+      <c r="AF60" s="46"/>
+      <c r="AG60" s="46"/>
+      <c r="AH60" s="46"/>
+      <c r="AI60" s="46"/>
+      <c r="AJ60" s="46"/>
+      <c r="AK60" s="47"/>
     </row>
     <row r="61" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
@@ -15276,45 +15201,45 @@
       <c r="AK128" s="1"/>
     </row>
     <row r="129" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="69" t="s">
+      <c r="A129" s="45" t="s">
         <v>531</v>
       </c>
-      <c r="B129" s="70"/>
-      <c r="C129" s="70"/>
-      <c r="D129" s="70"/>
-      <c r="E129" s="70"/>
-      <c r="F129" s="70"/>
-      <c r="G129" s="70"/>
-      <c r="H129" s="70"/>
-      <c r="I129" s="70"/>
-      <c r="J129" s="70"/>
-      <c r="K129" s="70"/>
-      <c r="L129" s="70"/>
-      <c r="M129" s="70"/>
-      <c r="N129" s="70"/>
-      <c r="O129" s="70"/>
-      <c r="P129" s="70"/>
-      <c r="Q129" s="70"/>
-      <c r="R129" s="70"/>
-      <c r="S129" s="70"/>
-      <c r="T129" s="70"/>
-      <c r="U129" s="70"/>
-      <c r="V129" s="70"/>
-      <c r="W129" s="70"/>
-      <c r="X129" s="70"/>
-      <c r="Y129" s="70"/>
-      <c r="Z129" s="70"/>
-      <c r="AA129" s="70"/>
-      <c r="AB129" s="70"/>
-      <c r="AC129" s="70"/>
-      <c r="AD129" s="70"/>
-      <c r="AE129" s="70"/>
-      <c r="AF129" s="70"/>
-      <c r="AG129" s="70"/>
-      <c r="AH129" s="70"/>
-      <c r="AI129" s="70"/>
-      <c r="AJ129" s="70"/>
-      <c r="AK129" s="71"/>
+      <c r="B129" s="46"/>
+      <c r="C129" s="46"/>
+      <c r="D129" s="46"/>
+      <c r="E129" s="46"/>
+      <c r="F129" s="46"/>
+      <c r="G129" s="46"/>
+      <c r="H129" s="46"/>
+      <c r="I129" s="46"/>
+      <c r="J129" s="46"/>
+      <c r="K129" s="46"/>
+      <c r="L129" s="46"/>
+      <c r="M129" s="46"/>
+      <c r="N129" s="46"/>
+      <c r="O129" s="46"/>
+      <c r="P129" s="46"/>
+      <c r="Q129" s="46"/>
+      <c r="R129" s="46"/>
+      <c r="S129" s="46"/>
+      <c r="T129" s="46"/>
+      <c r="U129" s="46"/>
+      <c r="V129" s="46"/>
+      <c r="W129" s="46"/>
+      <c r="X129" s="46"/>
+      <c r="Y129" s="46"/>
+      <c r="Z129" s="46"/>
+      <c r="AA129" s="46"/>
+      <c r="AB129" s="46"/>
+      <c r="AC129" s="46"/>
+      <c r="AD129" s="46"/>
+      <c r="AE129" s="46"/>
+      <c r="AF129" s="46"/>
+      <c r="AG129" s="46"/>
+      <c r="AH129" s="46"/>
+      <c r="AI129" s="46"/>
+      <c r="AJ129" s="46"/>
+      <c r="AK129" s="47"/>
     </row>
     <row r="130" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
@@ -15966,107 +15891,107 @@
       <c r="AK140" s="1"/>
     </row>
     <row r="141" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="69" t="s">
+      <c r="A141" s="45" t="s">
         <v>530</v>
       </c>
-      <c r="B141" s="70"/>
-      <c r="C141" s="70"/>
-      <c r="D141" s="70"/>
-      <c r="E141" s="70"/>
-      <c r="F141" s="70"/>
-      <c r="G141" s="70"/>
-      <c r="H141" s="70"/>
-      <c r="I141" s="70"/>
-      <c r="J141" s="70"/>
-      <c r="K141" s="70"/>
-      <c r="L141" s="70"/>
-      <c r="M141" s="70"/>
-      <c r="N141" s="70"/>
-      <c r="O141" s="70"/>
-      <c r="P141" s="70"/>
-      <c r="Q141" s="70"/>
-      <c r="R141" s="70"/>
-      <c r="S141" s="70"/>
-      <c r="T141" s="70"/>
-      <c r="U141" s="70"/>
-      <c r="V141" s="70"/>
-      <c r="W141" s="70"/>
-      <c r="X141" s="70"/>
-      <c r="Y141" s="70"/>
-      <c r="Z141" s="70"/>
-      <c r="AA141" s="70"/>
-      <c r="AB141" s="70"/>
-      <c r="AC141" s="70"/>
-      <c r="AD141" s="70"/>
-      <c r="AE141" s="70"/>
-      <c r="AF141" s="70"/>
-      <c r="AG141" s="70"/>
-      <c r="AH141" s="70"/>
-      <c r="AI141" s="70"/>
-      <c r="AJ141" s="70"/>
-      <c r="AK141" s="71"/>
+      <c r="B141" s="46"/>
+      <c r="C141" s="46"/>
+      <c r="D141" s="46"/>
+      <c r="E141" s="46"/>
+      <c r="F141" s="46"/>
+      <c r="G141" s="46"/>
+      <c r="H141" s="46"/>
+      <c r="I141" s="46"/>
+      <c r="J141" s="46"/>
+      <c r="K141" s="46"/>
+      <c r="L141" s="46"/>
+      <c r="M141" s="46"/>
+      <c r="N141" s="46"/>
+      <c r="O141" s="46"/>
+      <c r="P141" s="46"/>
+      <c r="Q141" s="46"/>
+      <c r="R141" s="46"/>
+      <c r="S141" s="46"/>
+      <c r="T141" s="46"/>
+      <c r="U141" s="46"/>
+      <c r="V141" s="46"/>
+      <c r="W141" s="46"/>
+      <c r="X141" s="46"/>
+      <c r="Y141" s="46"/>
+      <c r="Z141" s="46"/>
+      <c r="AA141" s="46"/>
+      <c r="AB141" s="46"/>
+      <c r="AC141" s="46"/>
+      <c r="AD141" s="46"/>
+      <c r="AE141" s="46"/>
+      <c r="AF141" s="46"/>
+      <c r="AG141" s="46"/>
+      <c r="AH141" s="46"/>
+      <c r="AI141" s="46"/>
+      <c r="AJ141" s="46"/>
+      <c r="AK141" s="47"/>
     </row>
     <row r="142" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A142" s="1" t="s">
+      <c r="A142" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B142" s="1" t="s">
+      <c r="B142" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="C142" s="1" t="s">
+      <c r="C142" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D142" s="3"/>
-      <c r="E142" s="3"/>
-      <c r="F142" s="1">
+      <c r="D142" s="7"/>
+      <c r="E142" s="7"/>
+      <c r="F142" s="2">
         <v>1</v>
       </c>
       <c r="G142" s="4">
         <v>1</v>
       </c>
-      <c r="H142" s="1"/>
+      <c r="H142" s="2"/>
       <c r="I142" s="2">
         <v>100</v>
       </c>
-      <c r="J142" s="1"/>
-      <c r="K142" s="1">
-        <v>1</v>
-      </c>
-      <c r="L142" s="1"/>
-      <c r="M142" s="1"/>
-      <c r="N142" s="1"/>
-      <c r="O142" s="1"/>
-      <c r="P142" s="1"/>
-      <c r="Q142" s="1"/>
-      <c r="R142" s="1"/>
-      <c r="S142" s="1"/>
-      <c r="T142" s="1"/>
-      <c r="U142" s="1"/>
-      <c r="V142" s="1"/>
-      <c r="W142" s="1"/>
-      <c r="X142" s="1"/>
-      <c r="Y142" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z142" s="1" t="s">
+      <c r="J142" s="2"/>
+      <c r="K142" s="2">
+        <v>1</v>
+      </c>
+      <c r="L142" s="2"/>
+      <c r="M142" s="2"/>
+      <c r="N142" s="2"/>
+      <c r="O142" s="2"/>
+      <c r="P142" s="2"/>
+      <c r="Q142" s="2"/>
+      <c r="R142" s="2"/>
+      <c r="S142" s="2"/>
+      <c r="T142" s="2"/>
+      <c r="U142" s="2"/>
+      <c r="V142" s="2"/>
+      <c r="W142" s="2"/>
+      <c r="X142" s="2"/>
+      <c r="Y142" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z142" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AA142" s="1"/>
-      <c r="AB142" s="1"/>
-      <c r="AC142" s="1"/>
-      <c r="AD142" s="1"/>
-      <c r="AE142" s="1"/>
-      <c r="AF142" s="1"/>
-      <c r="AG142" s="1"/>
-      <c r="AH142" s="1"/>
-      <c r="AI142" s="1" t="s">
+      <c r="AA142" s="2"/>
+      <c r="AB142" s="2"/>
+      <c r="AC142" s="2"/>
+      <c r="AD142" s="2"/>
+      <c r="AE142" s="2"/>
+      <c r="AF142" s="2"/>
+      <c r="AG142" s="2"/>
+      <c r="AH142" s="2"/>
+      <c r="AI142" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AJ142" s="1"/>
-      <c r="AK142" s="1"/>
+      <c r="AJ142" s="2"/>
+      <c r="AK142" s="2"/>
     </row>
     <row r="143" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A143" s="1" t="s">
+      <c r="A143" s="2" t="s">
         <v>427</v>
       </c>
       <c r="B143" s="2" t="s">
@@ -16101,7 +16026,7 @@
       <c r="S143" s="2"/>
       <c r="T143" s="2"/>
       <c r="U143" s="2"/>
-      <c r="V143" s="1" t="s">
+      <c r="V143" s="2" t="s">
         <v>216</v>
       </c>
       <c r="W143" s="2"/>
@@ -16124,10 +16049,10 @@
         <v>215</v>
       </c>
       <c r="AJ143" s="2"/>
-      <c r="AK143" s="1"/>
+      <c r="AK143" s="2"/>
     </row>
     <row r="144" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A144" s="1" t="s">
+      <c r="A144" s="2" t="s">
         <v>427</v>
       </c>
       <c r="B144" s="2" t="s">
@@ -16160,7 +16085,7 @@
       <c r="S144" s="6"/>
       <c r="T144" s="2"/>
       <c r="U144" s="2"/>
-      <c r="V144" s="1"/>
+      <c r="V144" s="2"/>
       <c r="W144" s="2"/>
       <c r="X144" s="2"/>
       <c r="Y144" s="2">
@@ -16187,10 +16112,10 @@
         <v>215</v>
       </c>
       <c r="AJ144" s="2"/>
-      <c r="AK144" s="1"/>
+      <c r="AK144" s="2"/>
     </row>
     <row r="145" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A145" s="1" t="s">
+      <c r="A145" s="2" t="s">
         <v>427</v>
       </c>
       <c r="B145" s="2" t="s">
@@ -16219,7 +16144,7 @@
       <c r="O145" s="2"/>
       <c r="P145" s="2"/>
       <c r="Q145" s="2"/>
-      <c r="R145" s="1" t="s">
+      <c r="R145" s="2" t="s">
         <v>217</v>
       </c>
       <c r="S145" s="6" t="s">
@@ -16227,7 +16152,7 @@
       </c>
       <c r="T145" s="2"/>
       <c r="U145" s="2"/>
-      <c r="V145" s="1" t="s">
+      <c r="V145" s="2" t="s">
         <v>218</v>
       </c>
       <c r="W145" s="2"/>
@@ -16250,10 +16175,10 @@
         <v>215</v>
       </c>
       <c r="AJ145" s="2"/>
-      <c r="AK145" s="1"/>
+      <c r="AK145" s="2"/>
     </row>
     <row r="146" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A146" s="1" t="s">
+      <c r="A146" s="2" t="s">
         <v>427</v>
       </c>
       <c r="B146" s="2" t="s">
@@ -16307,10 +16232,10 @@
         <v>215</v>
       </c>
       <c r="AJ146" s="2"/>
-      <c r="AK146" s="1"/>
+      <c r="AK146" s="2"/>
     </row>
     <row r="147" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A147" s="1" t="s">
+      <c r="A147" s="2" t="s">
         <v>427</v>
       </c>
       <c r="B147" s="2" t="s">
@@ -16325,7 +16250,7 @@
         <v>1</v>
       </c>
       <c r="G147" s="8"/>
-      <c r="H147" s="37" t="s">
+      <c r="H147" s="2" t="s">
         <v>653</v>
       </c>
       <c r="I147" s="2">
@@ -16334,12 +16259,12 @@
       <c r="J147" s="2"/>
       <c r="K147" s="2"/>
       <c r="L147" s="2"/>
-      <c r="M147" s="1" t="s">
+      <c r="M147" s="2" t="s">
         <v>85</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
-      <c r="P147" s="37" t="s">
+      <c r="P147" s="2" t="s">
         <v>725</v>
       </c>
       <c r="Q147" s="2"/>
@@ -16366,17 +16291,17 @@
       <c r="AH147" s="2"/>
       <c r="AI147" s="2"/>
       <c r="AJ147" s="2"/>
-      <c r="AK147" s="1"/>
+      <c r="AK147" s="2"/>
     </row>
     <row r="148" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A148" s="1"/>
+      <c r="A148" s="2"/>
       <c r="B148" s="2"/>
-      <c r="C148" s="37" t="s">
+      <c r="C148" s="2" t="s">
         <v>713</v>
       </c>
       <c r="D148" s="7"/>
       <c r="E148" s="7"/>
-      <c r="F148" s="37">
+      <c r="F148" s="2">
         <v>1</v>
       </c>
       <c r="G148" s="8"/>
@@ -16389,7 +16314,7 @@
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
       <c r="P148" s="2"/>
-      <c r="Q148" s="37">
+      <c r="Q148" s="2">
         <v>3</v>
       </c>
       <c r="R148" s="2"/>
@@ -16411,10 +16336,10 @@
       <c r="AH148" s="2"/>
       <c r="AI148" s="2"/>
       <c r="AJ148" s="2"/>
-      <c r="AK148" s="1"/>
+      <c r="AK148" s="2"/>
     </row>
     <row r="149" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A149" s="1" t="s">
+      <c r="A149" s="2" t="s">
         <v>427</v>
       </c>
       <c r="B149" s="2" t="s">
@@ -16447,7 +16372,7 @@
       <c r="S149" s="6"/>
       <c r="T149" s="2"/>
       <c r="U149" s="2"/>
-      <c r="V149" s="1"/>
+      <c r="V149" s="2"/>
       <c r="W149" s="2"/>
       <c r="X149" s="2"/>
       <c r="Y149" s="2">
@@ -16468,10 +16393,10 @@
         <v>215</v>
       </c>
       <c r="AJ149" s="2"/>
-      <c r="AK149" s="1"/>
+      <c r="AK149" s="2"/>
     </row>
     <row r="150" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A150" s="1" t="s">
+      <c r="A150" s="2" t="s">
         <v>427</v>
       </c>
       <c r="B150" s="2" t="s">
@@ -16500,7 +16425,7 @@
       <c r="O150" s="2"/>
       <c r="P150" s="2"/>
       <c r="Q150" s="2"/>
-      <c r="R150" s="1" t="s">
+      <c r="R150" s="2" t="s">
         <v>56</v>
       </c>
       <c r="S150" s="6" t="s">
@@ -16508,7 +16433,7 @@
       </c>
       <c r="T150" s="2"/>
       <c r="U150" s="2"/>
-      <c r="V150" s="1" t="s">
+      <c r="V150" s="2" t="s">
         <v>218</v>
       </c>
       <c r="W150" s="2"/>
@@ -16535,56 +16460,56 @@
         <v>215</v>
       </c>
       <c r="AJ150" s="2"/>
-      <c r="AK150" s="1"/>
+      <c r="AK150" s="2"/>
     </row>
     <row r="151" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A151" s="1" t="s">
+      <c r="A151" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B151" s="37" t="s">
+      <c r="B151" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="C151" s="37" t="s">
+      <c r="C151" s="2" t="s">
         <v>728</v>
       </c>
       <c r="D151" s="7"/>
       <c r="E151" s="7"/>
-      <c r="F151" s="37">
-        <v>1</v>
-      </c>
-      <c r="G151" s="68"/>
-      <c r="H151" s="37"/>
-      <c r="I151" s="37">
+      <c r="F151" s="2">
+        <v>1</v>
+      </c>
+      <c r="G151" s="8"/>
+      <c r="H151" s="2"/>
+      <c r="I151" s="2">
         <v>150</v>
       </c>
-      <c r="J151" s="37"/>
-      <c r="K151" s="37"/>
-      <c r="L151" s="37"/>
-      <c r="M151" s="64" t="s">
+      <c r="J151" s="2"/>
+      <c r="K151" s="2"/>
+      <c r="L151" s="2"/>
+      <c r="M151" s="52" t="s">
         <v>709</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
       <c r="P151" s="2"/>
       <c r="Q151" s="2"/>
-      <c r="R151" s="1"/>
+      <c r="R151" s="2"/>
       <c r="S151" s="6"/>
       <c r="T151" s="2"/>
       <c r="U151" s="2"/>
-      <c r="V151" s="1"/>
+      <c r="V151" s="2"/>
       <c r="W151" s="2"/>
       <c r="X151" s="2"/>
       <c r="Y151" s="2">
         <v>1</v>
       </c>
-      <c r="Z151" s="37" t="s">
+      <c r="Z151" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AA151" s="64" t="s">
+      <c r="AA151" s="52" t="s">
         <v>709</v>
       </c>
-      <c r="AB151" s="37"/>
-      <c r="AC151" s="37" t="s">
+      <c r="AB151" s="2"/>
+      <c r="AC151" s="2" t="s">
         <v>726</v>
       </c>
       <c r="AD151" s="2"/>
@@ -16594,10 +16519,10 @@
       <c r="AH151" s="2"/>
       <c r="AI151" s="2"/>
       <c r="AJ151" s="2"/>
-      <c r="AK151" s="1"/>
+      <c r="AK151" s="2"/>
     </row>
     <row r="152" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A152" s="1" t="s">
+      <c r="A152" s="2" t="s">
         <v>427</v>
       </c>
       <c r="B152" s="2" t="s">
@@ -16622,17 +16547,17 @@
       <c r="O152" s="2"/>
       <c r="P152" s="2"/>
       <c r="Q152" s="2"/>
-      <c r="R152" s="1"/>
-      <c r="S152" s="1"/>
-      <c r="T152" s="1"/>
-      <c r="U152" s="1"/>
-      <c r="V152" s="1"/>
-      <c r="W152" s="1"/>
-      <c r="X152" s="1"/>
+      <c r="R152" s="2"/>
+      <c r="S152" s="2"/>
+      <c r="T152" s="2"/>
+      <c r="U152" s="2"/>
+      <c r="V152" s="2"/>
+      <c r="W152" s="2"/>
+      <c r="X152" s="2"/>
       <c r="Y152" s="2">
         <v>1</v>
       </c>
-      <c r="Z152" s="1" t="s">
+      <c r="Z152" s="2" t="s">
         <v>222</v>
       </c>
       <c r="AA152" s="2"/>
@@ -16645,10 +16570,10 @@
       <c r="AH152" s="2"/>
       <c r="AI152" s="2"/>
       <c r="AJ152" s="2"/>
-      <c r="AK152" s="1"/>
+      <c r="AK152" s="2"/>
     </row>
     <row r="153" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A153" s="1" t="s">
+      <c r="A153" s="2" t="s">
         <v>427</v>
       </c>
       <c r="B153" s="2" t="s">
@@ -16673,17 +16598,17 @@
       <c r="O153" s="2"/>
       <c r="P153" s="2"/>
       <c r="Q153" s="2"/>
-      <c r="R153" s="1"/>
-      <c r="S153" s="1"/>
-      <c r="T153" s="1"/>
-      <c r="U153" s="1"/>
-      <c r="V153" s="1"/>
-      <c r="W153" s="1"/>
-      <c r="X153" s="1"/>
+      <c r="R153" s="2"/>
+      <c r="S153" s="2"/>
+      <c r="T153" s="2"/>
+      <c r="U153" s="2"/>
+      <c r="V153" s="2"/>
+      <c r="W153" s="2"/>
+      <c r="X153" s="2"/>
       <c r="Y153" s="2">
         <v>1</v>
       </c>
-      <c r="Z153" s="1" t="s">
+      <c r="Z153" s="2" t="s">
         <v>224</v>
       </c>
       <c r="AA153" s="2"/>
@@ -16698,10 +16623,10 @@
       <c r="AH153" s="2"/>
       <c r="AI153" s="2"/>
       <c r="AJ153" s="2"/>
-      <c r="AK153" s="1"/>
+      <c r="AK153" s="2"/>
     </row>
     <row r="154" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A154" s="1" t="s">
+      <c r="A154" s="2" t="s">
         <v>427</v>
       </c>
       <c r="B154" s="2" t="s">
@@ -16726,17 +16651,17 @@
       <c r="O154" s="2"/>
       <c r="P154" s="2"/>
       <c r="Q154" s="2"/>
-      <c r="R154" s="1"/>
-      <c r="S154" s="1"/>
-      <c r="T154" s="1"/>
-      <c r="U154" s="1"/>
-      <c r="V154" s="1"/>
-      <c r="W154" s="1"/>
-      <c r="X154" s="1"/>
+      <c r="R154" s="2"/>
+      <c r="S154" s="2"/>
+      <c r="T154" s="2"/>
+      <c r="U154" s="2"/>
+      <c r="V154" s="2"/>
+      <c r="W154" s="2"/>
+      <c r="X154" s="2"/>
       <c r="Y154" s="2">
         <v>1</v>
       </c>
-      <c r="Z154" s="1" t="s">
+      <c r="Z154" s="2" t="s">
         <v>227</v>
       </c>
       <c r="AA154" s="2"/>
@@ -16751,10 +16676,10 @@
       <c r="AH154" s="2"/>
       <c r="AI154" s="2"/>
       <c r="AJ154" s="2"/>
-      <c r="AK154" s="1"/>
+      <c r="AK154" s="2"/>
     </row>
     <row r="155" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A155" s="1" t="s">
+      <c r="A155" s="2" t="s">
         <v>427</v>
       </c>
       <c r="B155" s="2" t="s">
@@ -16779,17 +16704,17 @@
       <c r="O155" s="2"/>
       <c r="P155" s="2"/>
       <c r="Q155" s="2"/>
-      <c r="R155" s="1"/>
-      <c r="S155" s="1"/>
-      <c r="T155" s="1"/>
-      <c r="U155" s="1"/>
-      <c r="V155" s="1"/>
-      <c r="W155" s="1"/>
-      <c r="X155" s="1"/>
+      <c r="R155" s="2"/>
+      <c r="S155" s="2"/>
+      <c r="T155" s="2"/>
+      <c r="U155" s="2"/>
+      <c r="V155" s="2"/>
+      <c r="W155" s="2"/>
+      <c r="X155" s="2"/>
       <c r="Y155" s="2">
         <v>1</v>
       </c>
-      <c r="Z155" s="1" t="s">
+      <c r="Z155" s="2" t="s">
         <v>230</v>
       </c>
       <c r="AA155" s="2"/>
@@ -16804,10 +16729,10 @@
       <c r="AH155" s="2"/>
       <c r="AI155" s="2"/>
       <c r="AJ155" s="2"/>
-      <c r="AK155" s="1"/>
+      <c r="AK155" s="2"/>
     </row>
     <row r="156" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A156" s="1" t="s">
+      <c r="A156" s="2" t="s">
         <v>427</v>
       </c>
       <c r="B156" s="2" t="s">
@@ -16831,24 +16756,24 @@
       </c>
       <c r="K156" s="2"/>
       <c r="L156" s="2"/>
-      <c r="M156" s="63" t="s">
+      <c r="M156" s="52" t="s">
         <v>707</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
       <c r="P156" s="2"/>
       <c r="Q156" s="2"/>
-      <c r="R156" s="1"/>
-      <c r="S156" s="1"/>
-      <c r="T156" s="1"/>
-      <c r="U156" s="1"/>
-      <c r="V156" s="1"/>
-      <c r="W156" s="1"/>
-      <c r="X156" s="1"/>
+      <c r="R156" s="2"/>
+      <c r="S156" s="2"/>
+      <c r="T156" s="2"/>
+      <c r="U156" s="2"/>
+      <c r="V156" s="2"/>
+      <c r="W156" s="2"/>
+      <c r="X156" s="2"/>
       <c r="Y156" s="2">
         <v>1</v>
       </c>
-      <c r="Z156" s="27" t="s">
+      <c r="Z156" s="52" t="s">
         <v>707</v>
       </c>
       <c r="AA156" s="2"/>
@@ -16861,10 +16786,10 @@
       <c r="AH156" s="2"/>
       <c r="AI156" s="2"/>
       <c r="AJ156" s="2"/>
-      <c r="AK156" s="1"/>
+      <c r="AK156" s="2"/>
     </row>
     <row r="157" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A157" s="1" t="s">
+      <c r="A157" s="2" t="s">
         <v>427</v>
       </c>
       <c r="B157" s="2" t="s">
@@ -16888,24 +16813,24 @@
       </c>
       <c r="K157" s="2"/>
       <c r="L157" s="2"/>
-      <c r="M157" s="63" t="s">
+      <c r="M157" s="52" t="s">
         <v>133</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
       <c r="P157" s="2"/>
       <c r="Q157" s="2"/>
-      <c r="R157" s="1"/>
-      <c r="S157" s="1"/>
-      <c r="T157" s="1"/>
-      <c r="U157" s="1"/>
-      <c r="V157" s="1"/>
-      <c r="W157" s="1"/>
-      <c r="X157" s="1"/>
+      <c r="R157" s="2"/>
+      <c r="S157" s="2"/>
+      <c r="T157" s="2"/>
+      <c r="U157" s="2"/>
+      <c r="V157" s="2"/>
+      <c r="W157" s="2"/>
+      <c r="X157" s="2"/>
       <c r="Y157" s="2">
         <v>1</v>
       </c>
-      <c r="Z157" s="1" t="s">
+      <c r="Z157" s="2" t="s">
         <v>232</v>
       </c>
       <c r="AA157" s="2"/>
@@ -16918,48 +16843,48 @@
       <c r="AH157" s="2"/>
       <c r="AI157" s="2"/>
       <c r="AJ157" s="2"/>
-      <c r="AK157" s="1"/>
+      <c r="AK157" s="2"/>
     </row>
     <row r="158" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="72" t="s">
+      <c r="A158" s="48" t="s">
         <v>529</v>
       </c>
-      <c r="B158" s="73"/>
-      <c r="C158" s="73"/>
-      <c r="D158" s="73"/>
-      <c r="E158" s="73"/>
-      <c r="F158" s="73"/>
-      <c r="G158" s="73"/>
-      <c r="H158" s="73"/>
-      <c r="I158" s="73"/>
-      <c r="J158" s="73"/>
-      <c r="K158" s="73"/>
-      <c r="L158" s="73"/>
-      <c r="M158" s="73"/>
-      <c r="N158" s="73"/>
-      <c r="O158" s="73"/>
-      <c r="P158" s="73"/>
-      <c r="Q158" s="73"/>
-      <c r="R158" s="73"/>
-      <c r="S158" s="73"/>
-      <c r="T158" s="73"/>
-      <c r="U158" s="73"/>
-      <c r="V158" s="73"/>
-      <c r="W158" s="73"/>
-      <c r="X158" s="73"/>
-      <c r="Y158" s="73"/>
-      <c r="Z158" s="73"/>
-      <c r="AA158" s="73"/>
-      <c r="AB158" s="73"/>
-      <c r="AC158" s="73"/>
-      <c r="AD158" s="73"/>
-      <c r="AE158" s="73"/>
-      <c r="AF158" s="73"/>
-      <c r="AG158" s="73"/>
-      <c r="AH158" s="73"/>
-      <c r="AI158" s="73"/>
-      <c r="AJ158" s="73"/>
-      <c r="AK158" s="74"/>
+      <c r="B158" s="49"/>
+      <c r="C158" s="49"/>
+      <c r="D158" s="49"/>
+      <c r="E158" s="49"/>
+      <c r="F158" s="49"/>
+      <c r="G158" s="49"/>
+      <c r="H158" s="49"/>
+      <c r="I158" s="49"/>
+      <c r="J158" s="49"/>
+      <c r="K158" s="49"/>
+      <c r="L158" s="49"/>
+      <c r="M158" s="49"/>
+      <c r="N158" s="49"/>
+      <c r="O158" s="49"/>
+      <c r="P158" s="49"/>
+      <c r="Q158" s="49"/>
+      <c r="R158" s="49"/>
+      <c r="S158" s="49"/>
+      <c r="T158" s="49"/>
+      <c r="U158" s="49"/>
+      <c r="V158" s="49"/>
+      <c r="W158" s="49"/>
+      <c r="X158" s="49"/>
+      <c r="Y158" s="49"/>
+      <c r="Z158" s="49"/>
+      <c r="AA158" s="49"/>
+      <c r="AB158" s="49"/>
+      <c r="AC158" s="49"/>
+      <c r="AD158" s="49"/>
+      <c r="AE158" s="49"/>
+      <c r="AF158" s="49"/>
+      <c r="AG158" s="49"/>
+      <c r="AH158" s="49"/>
+      <c r="AI158" s="49"/>
+      <c r="AJ158" s="49"/>
+      <c r="AK158" s="50"/>
     </row>
     <row r="159" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
@@ -17196,45 +17121,45 @@
       <c r="AK162" s="1"/>
     </row>
     <row r="163" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="69" t="s">
+      <c r="A163" s="45" t="s">
         <v>528</v>
       </c>
-      <c r="B163" s="70"/>
-      <c r="C163" s="70"/>
-      <c r="D163" s="70"/>
-      <c r="E163" s="70"/>
-      <c r="F163" s="70"/>
-      <c r="G163" s="70"/>
-      <c r="H163" s="70"/>
-      <c r="I163" s="70"/>
-      <c r="J163" s="70"/>
-      <c r="K163" s="70"/>
-      <c r="L163" s="70"/>
-      <c r="M163" s="70"/>
-      <c r="N163" s="70"/>
-      <c r="O163" s="70"/>
-      <c r="P163" s="70"/>
-      <c r="Q163" s="70"/>
-      <c r="R163" s="70"/>
-      <c r="S163" s="70"/>
-      <c r="T163" s="70"/>
-      <c r="U163" s="70"/>
-      <c r="V163" s="70"/>
-      <c r="W163" s="70"/>
-      <c r="X163" s="70"/>
-      <c r="Y163" s="70"/>
-      <c r="Z163" s="70"/>
-      <c r="AA163" s="70"/>
-      <c r="AB163" s="70"/>
-      <c r="AC163" s="70"/>
-      <c r="AD163" s="70"/>
-      <c r="AE163" s="70"/>
-      <c r="AF163" s="70"/>
-      <c r="AG163" s="70"/>
-      <c r="AH163" s="70"/>
-      <c r="AI163" s="70"/>
-      <c r="AJ163" s="70"/>
-      <c r="AK163" s="71"/>
+      <c r="B163" s="46"/>
+      <c r="C163" s="46"/>
+      <c r="D163" s="46"/>
+      <c r="E163" s="46"/>
+      <c r="F163" s="46"/>
+      <c r="G163" s="46"/>
+      <c r="H163" s="46"/>
+      <c r="I163" s="46"/>
+      <c r="J163" s="46"/>
+      <c r="K163" s="46"/>
+      <c r="L163" s="46"/>
+      <c r="M163" s="46"/>
+      <c r="N163" s="46"/>
+      <c r="O163" s="46"/>
+      <c r="P163" s="46"/>
+      <c r="Q163" s="46"/>
+      <c r="R163" s="46"/>
+      <c r="S163" s="46"/>
+      <c r="T163" s="46"/>
+      <c r="U163" s="46"/>
+      <c r="V163" s="46"/>
+      <c r="W163" s="46"/>
+      <c r="X163" s="46"/>
+      <c r="Y163" s="46"/>
+      <c r="Z163" s="46"/>
+      <c r="AA163" s="46"/>
+      <c r="AB163" s="46"/>
+      <c r="AC163" s="46"/>
+      <c r="AD163" s="46"/>
+      <c r="AE163" s="46"/>
+      <c r="AF163" s="46"/>
+      <c r="AG163" s="46"/>
+      <c r="AH163" s="46"/>
+      <c r="AI163" s="46"/>
+      <c r="AJ163" s="46"/>
+      <c r="AK163" s="47"/>
     </row>
     <row r="164" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
@@ -17526,45 +17451,45 @@
       <c r="AK168" s="1"/>
     </row>
     <row r="169" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="69" t="s">
+      <c r="A169" s="45" t="s">
         <v>527</v>
       </c>
-      <c r="B169" s="70"/>
-      <c r="C169" s="70"/>
-      <c r="D169" s="70"/>
-      <c r="E169" s="70"/>
-      <c r="F169" s="70"/>
-      <c r="G169" s="70"/>
-      <c r="H169" s="70"/>
-      <c r="I169" s="70"/>
-      <c r="J169" s="70"/>
-      <c r="K169" s="70"/>
-      <c r="L169" s="70"/>
-      <c r="M169" s="70"/>
-      <c r="N169" s="70"/>
-      <c r="O169" s="70"/>
-      <c r="P169" s="70"/>
-      <c r="Q169" s="70"/>
-      <c r="R169" s="70"/>
-      <c r="S169" s="70"/>
-      <c r="T169" s="70"/>
-      <c r="U169" s="70"/>
-      <c r="V169" s="70"/>
-      <c r="W169" s="70"/>
-      <c r="X169" s="70"/>
-      <c r="Y169" s="70"/>
-      <c r="Z169" s="70"/>
-      <c r="AA169" s="70"/>
-      <c r="AB169" s="70"/>
-      <c r="AC169" s="70"/>
-      <c r="AD169" s="70"/>
-      <c r="AE169" s="70"/>
-      <c r="AF169" s="70"/>
-      <c r="AG169" s="70"/>
-      <c r="AH169" s="70"/>
-      <c r="AI169" s="70"/>
-      <c r="AJ169" s="70"/>
-      <c r="AK169" s="71"/>
+      <c r="B169" s="46"/>
+      <c r="C169" s="46"/>
+      <c r="D169" s="46"/>
+      <c r="E169" s="46"/>
+      <c r="F169" s="46"/>
+      <c r="G169" s="46"/>
+      <c r="H169" s="46"/>
+      <c r="I169" s="46"/>
+      <c r="J169" s="46"/>
+      <c r="K169" s="46"/>
+      <c r="L169" s="46"/>
+      <c r="M169" s="46"/>
+      <c r="N169" s="46"/>
+      <c r="O169" s="46"/>
+      <c r="P169" s="46"/>
+      <c r="Q169" s="46"/>
+      <c r="R169" s="46"/>
+      <c r="S169" s="46"/>
+      <c r="T169" s="46"/>
+      <c r="U169" s="46"/>
+      <c r="V169" s="46"/>
+      <c r="W169" s="46"/>
+      <c r="X169" s="46"/>
+      <c r="Y169" s="46"/>
+      <c r="Z169" s="46"/>
+      <c r="AA169" s="46"/>
+      <c r="AB169" s="46"/>
+      <c r="AC169" s="46"/>
+      <c r="AD169" s="46"/>
+      <c r="AE169" s="46"/>
+      <c r="AF169" s="46"/>
+      <c r="AG169" s="46"/>
+      <c r="AH169" s="46"/>
+      <c r="AI169" s="46"/>
+      <c r="AJ169" s="46"/>
+      <c r="AK169" s="47"/>
     </row>
     <row r="170" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
@@ -18027,45 +17952,45 @@
       <c r="AK177" s="1"/>
     </row>
     <row r="178" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A178" s="69" t="s">
+      <c r="A178" s="45" t="s">
         <v>526</v>
       </c>
-      <c r="B178" s="70"/>
-      <c r="C178" s="70"/>
-      <c r="D178" s="70"/>
-      <c r="E178" s="70"/>
-      <c r="F178" s="70"/>
-      <c r="G178" s="70"/>
-      <c r="H178" s="70"/>
-      <c r="I178" s="70"/>
-      <c r="J178" s="70"/>
-      <c r="K178" s="70"/>
-      <c r="L178" s="70"/>
-      <c r="M178" s="70"/>
-      <c r="N178" s="70"/>
-      <c r="O178" s="70"/>
-      <c r="P178" s="70"/>
-      <c r="Q178" s="70"/>
-      <c r="R178" s="70"/>
-      <c r="S178" s="70"/>
-      <c r="T178" s="70"/>
-      <c r="U178" s="70"/>
-      <c r="V178" s="70"/>
-      <c r="W178" s="70"/>
-      <c r="X178" s="70"/>
-      <c r="Y178" s="70"/>
-      <c r="Z178" s="70"/>
-      <c r="AA178" s="70"/>
-      <c r="AB178" s="70"/>
-      <c r="AC178" s="70"/>
-      <c r="AD178" s="70"/>
-      <c r="AE178" s="70"/>
-      <c r="AF178" s="70"/>
-      <c r="AG178" s="70"/>
-      <c r="AH178" s="70"/>
-      <c r="AI178" s="70"/>
-      <c r="AJ178" s="70"/>
-      <c r="AK178" s="71"/>
+      <c r="B178" s="46"/>
+      <c r="C178" s="46"/>
+      <c r="D178" s="46"/>
+      <c r="E178" s="46"/>
+      <c r="F178" s="46"/>
+      <c r="G178" s="46"/>
+      <c r="H178" s="46"/>
+      <c r="I178" s="46"/>
+      <c r="J178" s="46"/>
+      <c r="K178" s="46"/>
+      <c r="L178" s="46"/>
+      <c r="M178" s="46"/>
+      <c r="N178" s="46"/>
+      <c r="O178" s="46"/>
+      <c r="P178" s="46"/>
+      <c r="Q178" s="46"/>
+      <c r="R178" s="46"/>
+      <c r="S178" s="46"/>
+      <c r="T178" s="46"/>
+      <c r="U178" s="46"/>
+      <c r="V178" s="46"/>
+      <c r="W178" s="46"/>
+      <c r="X178" s="46"/>
+      <c r="Y178" s="46"/>
+      <c r="Z178" s="46"/>
+      <c r="AA178" s="46"/>
+      <c r="AB178" s="46"/>
+      <c r="AC178" s="46"/>
+      <c r="AD178" s="46"/>
+      <c r="AE178" s="46"/>
+      <c r="AF178" s="46"/>
+      <c r="AG178" s="46"/>
+      <c r="AH178" s="46"/>
+      <c r="AI178" s="46"/>
+      <c r="AJ178" s="46"/>
+      <c r="AK178" s="47"/>
     </row>
     <row r="179" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A179" s="26" t="s">
@@ -18092,7 +18017,7 @@
       <c r="J179" s="1"/>
       <c r="K179" s="1"/>
       <c r="L179" s="1"/>
-      <c r="M179" s="37" t="s">
+      <c r="M179" s="2" t="s">
         <v>467</v>
       </c>
       <c r="N179" s="1"/>
@@ -18113,7 +18038,7 @@
         <v>42</v>
       </c>
       <c r="AA179" s="1"/>
-      <c r="AB179" s="37">
+      <c r="AB179" s="2">
         <v>1</v>
       </c>
       <c r="AC179" s="1"/>
@@ -18153,7 +18078,7 @@
       <c r="J180" s="2"/>
       <c r="K180" s="2"/>
       <c r="L180" s="2"/>
-      <c r="M180" s="37" t="s">
+      <c r="M180" s="2" t="s">
         <v>469</v>
       </c>
       <c r="N180" s="2"/>
@@ -18212,7 +18137,7 @@
       <c r="J181" s="2"/>
       <c r="K181" s="2"/>
       <c r="L181" s="2"/>
-      <c r="M181" s="37" t="s">
+      <c r="M181" s="2" t="s">
         <v>471</v>
       </c>
       <c r="N181" s="2"/>
@@ -18473,48 +18398,48 @@
       <c r="AK185" s="1"/>
     </row>
     <row r="186" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A186" s="69" t="s">
+      <c r="A186" s="45" t="s">
         <v>534</v>
       </c>
-      <c r="B186" s="70"/>
-      <c r="C186" s="70"/>
-      <c r="D186" s="70"/>
-      <c r="E186" s="70"/>
-      <c r="F186" s="70"/>
-      <c r="G186" s="70"/>
-      <c r="H186" s="70"/>
-      <c r="I186" s="70"/>
-      <c r="J186" s="70"/>
-      <c r="K186" s="70"/>
-      <c r="L186" s="70"/>
-      <c r="M186" s="70"/>
-      <c r="N186" s="70"/>
-      <c r="O186" s="70"/>
-      <c r="P186" s="70"/>
-      <c r="Q186" s="70"/>
-      <c r="R186" s="70"/>
-      <c r="S186" s="70"/>
-      <c r="T186" s="70"/>
-      <c r="U186" s="70"/>
-      <c r="V186" s="70"/>
-      <c r="W186" s="70"/>
-      <c r="X186" s="70"/>
-      <c r="Y186" s="70"/>
-      <c r="Z186" s="70"/>
-      <c r="AA186" s="70"/>
-      <c r="AB186" s="70"/>
-      <c r="AC186" s="70"/>
-      <c r="AD186" s="70"/>
-      <c r="AE186" s="70"/>
-      <c r="AF186" s="70"/>
-      <c r="AG186" s="70"/>
-      <c r="AH186" s="70"/>
-      <c r="AI186" s="70"/>
-      <c r="AJ186" s="70"/>
-      <c r="AK186" s="71"/>
+      <c r="B186" s="46"/>
+      <c r="C186" s="46"/>
+      <c r="D186" s="46"/>
+      <c r="E186" s="46"/>
+      <c r="F186" s="46"/>
+      <c r="G186" s="46"/>
+      <c r="H186" s="46"/>
+      <c r="I186" s="46"/>
+      <c r="J186" s="46"/>
+      <c r="K186" s="46"/>
+      <c r="L186" s="46"/>
+      <c r="M186" s="46"/>
+      <c r="N186" s="46"/>
+      <c r="O186" s="46"/>
+      <c r="P186" s="46"/>
+      <c r="Q186" s="46"/>
+      <c r="R186" s="46"/>
+      <c r="S186" s="46"/>
+      <c r="T186" s="46"/>
+      <c r="U186" s="46"/>
+      <c r="V186" s="46"/>
+      <c r="W186" s="46"/>
+      <c r="X186" s="46"/>
+      <c r="Y186" s="46"/>
+      <c r="Z186" s="46"/>
+      <c r="AA186" s="46"/>
+      <c r="AB186" s="46"/>
+      <c r="AC186" s="46"/>
+      <c r="AD186" s="46"/>
+      <c r="AE186" s="46"/>
+      <c r="AF186" s="46"/>
+      <c r="AG186" s="46"/>
+      <c r="AH186" s="46"/>
+      <c r="AI186" s="46"/>
+      <c r="AJ186" s="46"/>
+      <c r="AK186" s="47"/>
     </row>
     <row r="187" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A187" s="1" t="s">
+      <c r="A187" s="2" t="s">
         <v>513</v>
       </c>
       <c r="B187" s="26" t="s">
@@ -18523,55 +18448,55 @@
       <c r="C187" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="D187" s="3"/>
-      <c r="E187" s="3"/>
-      <c r="F187" s="1">
+      <c r="D187" s="7"/>
+      <c r="E187" s="7"/>
+      <c r="F187" s="2">
         <v>1</v>
       </c>
       <c r="G187" s="4">
         <v>1</v>
       </c>
-      <c r="H187" s="1"/>
+      <c r="H187" s="2"/>
       <c r="I187" s="2">
         <v>120</v>
       </c>
-      <c r="J187" s="1"/>
-      <c r="K187" s="1">
-        <v>1</v>
-      </c>
-      <c r="L187" s="1"/>
-      <c r="M187" s="1"/>
-      <c r="N187" s="1"/>
-      <c r="O187" s="1"/>
-      <c r="P187" s="1"/>
-      <c r="Q187" s="1"/>
-      <c r="R187" s="1"/>
-      <c r="S187" s="1"/>
-      <c r="T187" s="1"/>
-      <c r="U187" s="1"/>
-      <c r="V187" s="1"/>
-      <c r="W187" s="1"/>
-      <c r="X187" s="1"/>
-      <c r="Y187" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z187" s="1" t="s">
+      <c r="J187" s="2"/>
+      <c r="K187" s="2">
+        <v>1</v>
+      </c>
+      <c r="L187" s="2"/>
+      <c r="M187" s="2"/>
+      <c r="N187" s="2"/>
+      <c r="O187" s="2"/>
+      <c r="P187" s="2"/>
+      <c r="Q187" s="2"/>
+      <c r="R187" s="2"/>
+      <c r="S187" s="2"/>
+      <c r="T187" s="2"/>
+      <c r="U187" s="2"/>
+      <c r="V187" s="2"/>
+      <c r="W187" s="2"/>
+      <c r="X187" s="2"/>
+      <c r="Y187" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z187" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AA187" s="1"/>
-      <c r="AB187" s="1"/>
-      <c r="AC187" s="1"/>
-      <c r="AD187" s="1"/>
-      <c r="AE187" s="1"/>
-      <c r="AF187" s="1"/>
-      <c r="AG187" s="1"/>
-      <c r="AH187" s="1"/>
-      <c r="AI187" s="1"/>
-      <c r="AJ187" s="1"/>
-      <c r="AK187" s="1"/>
+      <c r="AA187" s="2"/>
+      <c r="AB187" s="2"/>
+      <c r="AC187" s="2"/>
+      <c r="AD187" s="2"/>
+      <c r="AE187" s="2"/>
+      <c r="AF187" s="2"/>
+      <c r="AG187" s="2"/>
+      <c r="AH187" s="2"/>
+      <c r="AI187" s="2"/>
+      <c r="AJ187" s="2"/>
+      <c r="AK187" s="2"/>
     </row>
     <row r="188" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A188" s="1" t="s">
+      <c r="A188" s="2" t="s">
         <v>513</v>
       </c>
       <c r="B188" s="26" t="s">
@@ -18623,10 +18548,10 @@
       <c r="AH188" s="2"/>
       <c r="AI188" s="2"/>
       <c r="AJ188" s="2"/>
-      <c r="AK188" s="1"/>
+      <c r="AK188" s="2"/>
     </row>
     <row r="189" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A189" s="1" t="s">
+      <c r="A189" s="2" t="s">
         <v>513</v>
       </c>
       <c r="B189" s="26" t="s">
@@ -18684,10 +18609,10 @@
       <c r="AH189" s="2"/>
       <c r="AI189" s="2"/>
       <c r="AJ189" s="2"/>
-      <c r="AK189" s="1"/>
+      <c r="AK189" s="2"/>
     </row>
     <row r="190" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A190" s="1" t="s">
+      <c r="A190" s="2" t="s">
         <v>513</v>
       </c>
       <c r="B190" s="26" t="s">
@@ -18709,7 +18634,7 @@
       <c r="J190" s="2"/>
       <c r="K190" s="2"/>
       <c r="L190" s="2"/>
-      <c r="M190" s="1" t="s">
+      <c r="M190" s="2" t="s">
         <v>68</v>
       </c>
       <c r="N190" s="2"/>
@@ -18743,10 +18668,10 @@
       <c r="AH190" s="2"/>
       <c r="AI190" s="2"/>
       <c r="AJ190" s="2"/>
-      <c r="AK190" s="1"/>
+      <c r="AK190" s="2"/>
     </row>
     <row r="191" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A191" s="1" t="s">
+      <c r="A191" s="2" t="s">
         <v>513</v>
       </c>
       <c r="B191" s="26" t="s">
@@ -18798,10 +18723,10 @@
       <c r="AH191" s="2"/>
       <c r="AI191" s="2"/>
       <c r="AJ191" s="2"/>
-      <c r="AK191" s="1"/>
+      <c r="AK191" s="2"/>
     </row>
     <row r="192" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A192" s="1" t="s">
+      <c r="A192" s="2" t="s">
         <v>513</v>
       </c>
       <c r="B192" s="26" t="s">
@@ -18851,10 +18776,10 @@
       <c r="AH192" s="2"/>
       <c r="AI192" s="2"/>
       <c r="AJ192" s="2"/>
-      <c r="AK192" s="1"/>
+      <c r="AK192" s="2"/>
     </row>
     <row r="193" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A193" s="1" t="s">
+      <c r="A193" s="2" t="s">
         <v>513</v>
       </c>
       <c r="B193" s="26" t="s">
@@ -18912,10 +18837,10 @@
       <c r="AH193" s="2"/>
       <c r="AI193" s="2"/>
       <c r="AJ193" s="2"/>
-      <c r="AK193" s="1"/>
+      <c r="AK193" s="2"/>
     </row>
     <row r="194" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A194" s="1" t="s">
+      <c r="A194" s="2" t="s">
         <v>513</v>
       </c>
       <c r="B194" s="26" t="s">
@@ -18973,122 +18898,122 @@
       <c r="AH194" s="2"/>
       <c r="AI194" s="2"/>
       <c r="AJ194" s="2"/>
-      <c r="AK194" s="1"/>
+      <c r="AK194" s="2"/>
     </row>
     <row r="195" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A195" s="46" t="s">
+      <c r="A195" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="B195" s="57" t="s">
+      <c r="B195" s="26" t="s">
         <v>629</v>
       </c>
-      <c r="C195" s="57" t="s">
+      <c r="C195" s="26" t="s">
         <v>646</v>
       </c>
-      <c r="D195" s="59"/>
-      <c r="E195" s="59"/>
-      <c r="F195" s="46">
-        <v>1</v>
-      </c>
-      <c r="G195" s="56"/>
-      <c r="H195" s="46"/>
-      <c r="I195" s="46">
+      <c r="D195" s="7"/>
+      <c r="E195" s="7"/>
+      <c r="F195" s="2">
+        <v>1</v>
+      </c>
+      <c r="G195" s="4"/>
+      <c r="H195" s="2"/>
+      <c r="I195" s="2">
         <v>180</v>
       </c>
-      <c r="J195" s="46"/>
-      <c r="K195" s="46"/>
-      <c r="L195" s="46">
-        <v>1</v>
-      </c>
-      <c r="M195" s="46" t="s">
+      <c r="J195" s="2"/>
+      <c r="K195" s="2"/>
+      <c r="L195" s="2">
+        <v>1</v>
+      </c>
+      <c r="M195" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="N195" s="46"/>
-      <c r="O195" s="46"/>
-      <c r="P195" s="46"/>
-      <c r="Q195" s="46"/>
-      <c r="R195" s="46" t="s">
+      <c r="N195" s="2"/>
+      <c r="O195" s="2"/>
+      <c r="P195" s="2"/>
+      <c r="Q195" s="2"/>
+      <c r="R195" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="S195" s="46" t="s">
+      <c r="S195" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="T195" s="46"/>
-      <c r="U195" s="46"/>
-      <c r="V195" s="46"/>
-      <c r="W195" s="46"/>
-      <c r="X195" s="46"/>
-      <c r="Y195" s="46">
-        <v>1</v>
-      </c>
-      <c r="Z195" s="46" t="s">
+      <c r="T195" s="2"/>
+      <c r="U195" s="2"/>
+      <c r="V195" s="2"/>
+      <c r="W195" s="2"/>
+      <c r="X195" s="2"/>
+      <c r="Y195" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z195" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="AA195" s="46"/>
-      <c r="AB195" s="46"/>
-      <c r="AC195" s="46" t="s">
+      <c r="AA195" s="2"/>
+      <c r="AB195" s="2"/>
+      <c r="AC195" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="AD195" s="46"/>
-      <c r="AE195" s="46"/>
-      <c r="AF195" s="46"/>
-      <c r="AG195" s="46"/>
-      <c r="AH195" s="57"/>
-      <c r="AI195" s="57"/>
-      <c r="AJ195" s="46"/>
-      <c r="AK195" s="1"/>
+      <c r="AD195" s="2"/>
+      <c r="AE195" s="2"/>
+      <c r="AF195" s="2"/>
+      <c r="AG195" s="2"/>
+      <c r="AH195" s="26"/>
+      <c r="AI195" s="26"/>
+      <c r="AJ195" s="2"/>
+      <c r="AK195" s="2"/>
     </row>
     <row r="196" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A196" s="46" t="s">
+      <c r="A196" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="B196" s="57" t="s">
+      <c r="B196" s="26" t="s">
         <v>629</v>
       </c>
-      <c r="C196" s="57" t="s">
+      <c r="C196" s="26" t="s">
         <v>651</v>
       </c>
-      <c r="D196" s="59"/>
-      <c r="E196" s="59"/>
-      <c r="F196" s="46">
-        <v>1</v>
-      </c>
-      <c r="G196" s="58"/>
-      <c r="H196" s="46"/>
-      <c r="I196" s="46"/>
-      <c r="J196" s="46"/>
-      <c r="K196" s="46"/>
-      <c r="L196" s="46">
-        <v>1</v>
-      </c>
-      <c r="M196" s="46"/>
-      <c r="N196" s="46"/>
-      <c r="O196" s="46"/>
-      <c r="P196" s="46"/>
-      <c r="Q196" s="46"/>
-      <c r="R196" s="46"/>
-      <c r="S196" s="46"/>
-      <c r="T196" s="46"/>
-      <c r="U196" s="46"/>
-      <c r="V196" s="46"/>
-      <c r="W196" s="46"/>
-      <c r="X196" s="46"/>
-      <c r="Y196" s="46"/>
-      <c r="Z196" s="46"/>
-      <c r="AA196" s="46"/>
-      <c r="AB196" s="46"/>
-      <c r="AC196" s="46"/>
-      <c r="AD196" s="46"/>
-      <c r="AE196" s="46"/>
-      <c r="AF196" s="46"/>
-      <c r="AG196" s="46"/>
-      <c r="AH196" s="46"/>
-      <c r="AI196" s="46"/>
-      <c r="AJ196" s="46"/>
-      <c r="AK196" s="1"/>
+      <c r="D196" s="7"/>
+      <c r="E196" s="7"/>
+      <c r="F196" s="2">
+        <v>1</v>
+      </c>
+      <c r="G196" s="8"/>
+      <c r="H196" s="2"/>
+      <c r="I196" s="2"/>
+      <c r="J196" s="2"/>
+      <c r="K196" s="2"/>
+      <c r="L196" s="2">
+        <v>1</v>
+      </c>
+      <c r="M196" s="2"/>
+      <c r="N196" s="2"/>
+      <c r="O196" s="2"/>
+      <c r="P196" s="2"/>
+      <c r="Q196" s="2"/>
+      <c r="R196" s="2"/>
+      <c r="S196" s="2"/>
+      <c r="T196" s="2"/>
+      <c r="U196" s="2"/>
+      <c r="V196" s="2"/>
+      <c r="W196" s="2"/>
+      <c r="X196" s="2"/>
+      <c r="Y196" s="2"/>
+      <c r="Z196" s="2"/>
+      <c r="AA196" s="2"/>
+      <c r="AB196" s="2"/>
+      <c r="AC196" s="2"/>
+      <c r="AD196" s="2"/>
+      <c r="AE196" s="2"/>
+      <c r="AF196" s="2"/>
+      <c r="AG196" s="2"/>
+      <c r="AH196" s="2"/>
+      <c r="AI196" s="2"/>
+      <c r="AJ196" s="2"/>
+      <c r="AK196" s="2"/>
     </row>
     <row r="197" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A197" s="1"/>
+      <c r="A197" s="2"/>
       <c r="B197" s="26"/>
       <c r="C197" s="26" t="s">
         <v>536</v>
@@ -19108,7 +19033,7 @@
       </c>
       <c r="K197" s="2"/>
       <c r="L197" s="2"/>
-      <c r="M197" s="37" t="s">
+      <c r="M197" s="2" t="s">
         <v>553</v>
       </c>
       <c r="N197" s="2"/>
@@ -19134,10 +19059,10 @@
       <c r="AH197" s="2"/>
       <c r="AI197" s="2"/>
       <c r="AJ197" s="2"/>
-      <c r="AK197" s="1"/>
+      <c r="AK197" s="2"/>
     </row>
     <row r="198" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A198" s="1"/>
+      <c r="A198" s="2"/>
       <c r="B198" s="26"/>
       <c r="C198" s="26" t="s">
         <v>537</v>
@@ -19157,7 +19082,7 @@
       </c>
       <c r="K198" s="2"/>
       <c r="L198" s="2"/>
-      <c r="M198" s="37" t="s">
+      <c r="M198" s="2" t="s">
         <v>554</v>
       </c>
       <c r="N198" s="2"/>
@@ -19183,26 +19108,26 @@
       <c r="AH198" s="2"/>
       <c r="AI198" s="2"/>
       <c r="AJ198" s="2"/>
-      <c r="AK198" s="1"/>
+      <c r="AK198" s="2"/>
     </row>
     <row r="199" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A199" s="46" t="s">
+      <c r="A199" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="B199" s="57" t="s">
+      <c r="B199" s="26" t="s">
         <v>662</v>
       </c>
-      <c r="C199" s="62" t="s">
+      <c r="C199" s="26" t="s">
         <v>678</v>
       </c>
       <c r="D199" s="7"/>
       <c r="E199" s="7"/>
-      <c r="F199" s="37">
+      <c r="F199" s="2">
         <v>1</v>
       </c>
       <c r="G199" s="8"/>
       <c r="H199" s="2"/>
-      <c r="I199" s="37">
+      <c r="I199" s="2">
         <v>80</v>
       </c>
       <c r="J199" s="2" t="s">
@@ -19210,7 +19135,7 @@
       </c>
       <c r="K199" s="2"/>
       <c r="L199" s="2"/>
-      <c r="M199" s="37" t="s">
+      <c r="M199" s="2" t="s">
         <v>677</v>
       </c>
       <c r="N199" s="2"/>
@@ -19236,22 +19161,22 @@
       <c r="AH199" s="2"/>
       <c r="AI199" s="2"/>
       <c r="AJ199" s="2"/>
-      <c r="AK199" s="1"/>
+      <c r="AK199" s="2"/>
     </row>
     <row r="200" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A200" s="46"/>
-      <c r="B200" s="57"/>
-      <c r="C200" s="62" t="s">
+      <c r="A200" s="2"/>
+      <c r="B200" s="26"/>
+      <c r="C200" s="26" t="s">
         <v>698</v>
       </c>
       <c r="D200" s="7"/>
       <c r="E200" s="7"/>
-      <c r="F200" s="37">
+      <c r="F200" s="2">
         <v>1</v>
       </c>
       <c r="G200" s="8"/>
       <c r="H200" s="2"/>
-      <c r="I200" s="37">
+      <c r="I200" s="2">
         <v>80</v>
       </c>
       <c r="J200" s="2" t="s">
@@ -19259,7 +19184,7 @@
       </c>
       <c r="K200" s="2"/>
       <c r="L200" s="2"/>
-      <c r="M200" s="37" t="s">
+      <c r="M200" s="2" t="s">
         <v>699</v>
       </c>
       <c r="N200" s="2"/>
@@ -19285,48 +19210,48 @@
       <c r="AH200" s="2"/>
       <c r="AI200" s="2"/>
       <c r="AJ200" s="2"/>
-      <c r="AK200" s="1"/>
+      <c r="AK200" s="2"/>
     </row>
     <row r="201" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="69" t="s">
+      <c r="A201" s="45" t="s">
         <v>535</v>
       </c>
-      <c r="B201" s="70"/>
-      <c r="C201" s="70"/>
-      <c r="D201" s="70"/>
-      <c r="E201" s="70"/>
-      <c r="F201" s="70"/>
-      <c r="G201" s="70"/>
-      <c r="H201" s="70"/>
-      <c r="I201" s="70"/>
-      <c r="J201" s="70"/>
-      <c r="K201" s="70"/>
-      <c r="L201" s="70"/>
-      <c r="M201" s="70"/>
-      <c r="N201" s="70"/>
-      <c r="O201" s="70"/>
-      <c r="P201" s="70"/>
-      <c r="Q201" s="70"/>
-      <c r="R201" s="70"/>
-      <c r="S201" s="70"/>
-      <c r="T201" s="70"/>
-      <c r="U201" s="70"/>
-      <c r="V201" s="70"/>
-      <c r="W201" s="70"/>
-      <c r="X201" s="70"/>
-      <c r="Y201" s="70"/>
-      <c r="Z201" s="70"/>
-      <c r="AA201" s="70"/>
-      <c r="AB201" s="70"/>
-      <c r="AC201" s="70"/>
-      <c r="AD201" s="70"/>
-      <c r="AE201" s="70"/>
-      <c r="AF201" s="70"/>
-      <c r="AG201" s="70"/>
-      <c r="AH201" s="70"/>
-      <c r="AI201" s="70"/>
-      <c r="AJ201" s="70"/>
-      <c r="AK201" s="71"/>
+      <c r="B201" s="46"/>
+      <c r="C201" s="46"/>
+      <c r="D201" s="46"/>
+      <c r="E201" s="46"/>
+      <c r="F201" s="46"/>
+      <c r="G201" s="46"/>
+      <c r="H201" s="46"/>
+      <c r="I201" s="46"/>
+      <c r="J201" s="46"/>
+      <c r="K201" s="46"/>
+      <c r="L201" s="46"/>
+      <c r="M201" s="46"/>
+      <c r="N201" s="46"/>
+      <c r="O201" s="46"/>
+      <c r="P201" s="46"/>
+      <c r="Q201" s="46"/>
+      <c r="R201" s="46"/>
+      <c r="S201" s="46"/>
+      <c r="T201" s="46"/>
+      <c r="U201" s="46"/>
+      <c r="V201" s="46"/>
+      <c r="W201" s="46"/>
+      <c r="X201" s="46"/>
+      <c r="Y201" s="46"/>
+      <c r="Z201" s="46"/>
+      <c r="AA201" s="46"/>
+      <c r="AB201" s="46"/>
+      <c r="AC201" s="46"/>
+      <c r="AD201" s="46"/>
+      <c r="AE201" s="46"/>
+      <c r="AF201" s="46"/>
+      <c r="AG201" s="46"/>
+      <c r="AH201" s="46"/>
+      <c r="AI201" s="46"/>
+      <c r="AJ201" s="46"/>
+      <c r="AK201" s="47"/>
     </row>
     <row r="202" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
@@ -19556,7 +19481,7 @@
       <c r="A206" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="B206" s="38" t="s">
+      <c r="B206" s="37" t="s">
         <v>500</v>
       </c>
       <c r="C206" s="26" t="s">
@@ -19661,45 +19586,45 @@
       <c r="AK207" s="1"/>
     </row>
     <row r="208" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="69" t="s">
+      <c r="A208" s="45" t="s">
         <v>549</v>
       </c>
-      <c r="B208" s="70"/>
-      <c r="C208" s="70"/>
-      <c r="D208" s="70"/>
-      <c r="E208" s="70"/>
-      <c r="F208" s="70"/>
-      <c r="G208" s="70"/>
-      <c r="H208" s="70"/>
-      <c r="I208" s="70"/>
-      <c r="J208" s="70"/>
-      <c r="K208" s="70"/>
-      <c r="L208" s="70"/>
-      <c r="M208" s="70"/>
-      <c r="N208" s="70"/>
-      <c r="O208" s="70"/>
-      <c r="P208" s="70"/>
-      <c r="Q208" s="70"/>
-      <c r="R208" s="70"/>
-      <c r="S208" s="70"/>
-      <c r="T208" s="70"/>
-      <c r="U208" s="70"/>
-      <c r="V208" s="70"/>
-      <c r="W208" s="70"/>
-      <c r="X208" s="70"/>
-      <c r="Y208" s="70"/>
-      <c r="Z208" s="70"/>
-      <c r="AA208" s="70"/>
-      <c r="AB208" s="70"/>
-      <c r="AC208" s="70"/>
-      <c r="AD208" s="70"/>
-      <c r="AE208" s="70"/>
-      <c r="AF208" s="70"/>
-      <c r="AG208" s="70"/>
-      <c r="AH208" s="70"/>
-      <c r="AI208" s="70"/>
-      <c r="AJ208" s="70"/>
-      <c r="AK208" s="71"/>
+      <c r="B208" s="46"/>
+      <c r="C208" s="46"/>
+      <c r="D208" s="46"/>
+      <c r="E208" s="46"/>
+      <c r="F208" s="46"/>
+      <c r="G208" s="46"/>
+      <c r="H208" s="46"/>
+      <c r="I208" s="46"/>
+      <c r="J208" s="46"/>
+      <c r="K208" s="46"/>
+      <c r="L208" s="46"/>
+      <c r="M208" s="46"/>
+      <c r="N208" s="46"/>
+      <c r="O208" s="46"/>
+      <c r="P208" s="46"/>
+      <c r="Q208" s="46"/>
+      <c r="R208" s="46"/>
+      <c r="S208" s="46"/>
+      <c r="T208" s="46"/>
+      <c r="U208" s="46"/>
+      <c r="V208" s="46"/>
+      <c r="W208" s="46"/>
+      <c r="X208" s="46"/>
+      <c r="Y208" s="46"/>
+      <c r="Z208" s="46"/>
+      <c r="AA208" s="46"/>
+      <c r="AB208" s="46"/>
+      <c r="AC208" s="46"/>
+      <c r="AD208" s="46"/>
+      <c r="AE208" s="46"/>
+      <c r="AF208" s="46"/>
+      <c r="AG208" s="46"/>
+      <c r="AH208" s="46"/>
+      <c r="AI208" s="46"/>
+      <c r="AJ208" s="46"/>
+      <c r="AK208" s="47"/>
     </row>
     <row r="209" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
@@ -20038,45 +19963,45 @@
       <c r="AK214" s="1"/>
     </row>
     <row r="215" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="69" t="s">
+      <c r="A215" s="45" t="s">
         <v>740</v>
       </c>
-      <c r="B215" s="70"/>
-      <c r="C215" s="70"/>
-      <c r="D215" s="70"/>
-      <c r="E215" s="70"/>
-      <c r="F215" s="70"/>
-      <c r="G215" s="70"/>
-      <c r="H215" s="70"/>
-      <c r="I215" s="70"/>
-      <c r="J215" s="70"/>
-      <c r="K215" s="70"/>
-      <c r="L215" s="70"/>
-      <c r="M215" s="70"/>
-      <c r="N215" s="70"/>
-      <c r="O215" s="70"/>
-      <c r="P215" s="70"/>
-      <c r="Q215" s="70"/>
-      <c r="R215" s="70"/>
-      <c r="S215" s="70"/>
-      <c r="T215" s="70"/>
-      <c r="U215" s="70"/>
-      <c r="V215" s="70"/>
-      <c r="W215" s="70"/>
-      <c r="X215" s="70"/>
-      <c r="Y215" s="70"/>
-      <c r="Z215" s="70"/>
-      <c r="AA215" s="70"/>
-      <c r="AB215" s="70"/>
-      <c r="AC215" s="70"/>
-      <c r="AD215" s="70"/>
-      <c r="AE215" s="70"/>
-      <c r="AF215" s="70"/>
-      <c r="AG215" s="70"/>
-      <c r="AH215" s="70"/>
-      <c r="AI215" s="70"/>
-      <c r="AJ215" s="70"/>
-      <c r="AK215" s="71"/>
+      <c r="B215" s="46"/>
+      <c r="C215" s="46"/>
+      <c r="D215" s="46"/>
+      <c r="E215" s="46"/>
+      <c r="F215" s="46"/>
+      <c r="G215" s="46"/>
+      <c r="H215" s="46"/>
+      <c r="I215" s="46"/>
+      <c r="J215" s="46"/>
+      <c r="K215" s="46"/>
+      <c r="L215" s="46"/>
+      <c r="M215" s="46"/>
+      <c r="N215" s="46"/>
+      <c r="O215" s="46"/>
+      <c r="P215" s="46"/>
+      <c r="Q215" s="46"/>
+      <c r="R215" s="46"/>
+      <c r="S215" s="46"/>
+      <c r="T215" s="46"/>
+      <c r="U215" s="46"/>
+      <c r="V215" s="46"/>
+      <c r="W215" s="46"/>
+      <c r="X215" s="46"/>
+      <c r="Y215" s="46"/>
+      <c r="Z215" s="46"/>
+      <c r="AA215" s="46"/>
+      <c r="AB215" s="46"/>
+      <c r="AC215" s="46"/>
+      <c r="AD215" s="46"/>
+      <c r="AE215" s="46"/>
+      <c r="AF215" s="46"/>
+      <c r="AG215" s="46"/>
+      <c r="AH215" s="46"/>
+      <c r="AI215" s="46"/>
+      <c r="AJ215" s="46"/>
+      <c r="AK215" s="47"/>
     </row>
     <row r="216" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
@@ -20686,45 +20611,45 @@
       <c r="AK226" s="1"/>
     </row>
     <row r="227" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A227" s="69" t="s">
+      <c r="A227" s="45" t="s">
         <v>741</v>
       </c>
-      <c r="B227" s="70"/>
-      <c r="C227" s="70"/>
-      <c r="D227" s="70"/>
-      <c r="E227" s="70"/>
-      <c r="F227" s="70"/>
-      <c r="G227" s="70"/>
-      <c r="H227" s="70"/>
-      <c r="I227" s="70"/>
-      <c r="J227" s="70"/>
-      <c r="K227" s="70"/>
-      <c r="L227" s="70"/>
-      <c r="M227" s="70"/>
-      <c r="N227" s="70"/>
-      <c r="O227" s="70"/>
-      <c r="P227" s="70"/>
-      <c r="Q227" s="70"/>
-      <c r="R227" s="70"/>
-      <c r="S227" s="70"/>
-      <c r="T227" s="70"/>
-      <c r="U227" s="70"/>
-      <c r="V227" s="70"/>
-      <c r="W227" s="70"/>
-      <c r="X227" s="70"/>
-      <c r="Y227" s="70"/>
-      <c r="Z227" s="70"/>
-      <c r="AA227" s="70"/>
-      <c r="AB227" s="70"/>
-      <c r="AC227" s="70"/>
-      <c r="AD227" s="70"/>
-      <c r="AE227" s="70"/>
-      <c r="AF227" s="70"/>
-      <c r="AG227" s="70"/>
-      <c r="AH227" s="70"/>
-      <c r="AI227" s="70"/>
-      <c r="AJ227" s="70"/>
-      <c r="AK227" s="71"/>
+      <c r="B227" s="46"/>
+      <c r="C227" s="46"/>
+      <c r="D227" s="46"/>
+      <c r="E227" s="46"/>
+      <c r="F227" s="46"/>
+      <c r="G227" s="46"/>
+      <c r="H227" s="46"/>
+      <c r="I227" s="46"/>
+      <c r="J227" s="46"/>
+      <c r="K227" s="46"/>
+      <c r="L227" s="46"/>
+      <c r="M227" s="46"/>
+      <c r="N227" s="46"/>
+      <c r="O227" s="46"/>
+      <c r="P227" s="46"/>
+      <c r="Q227" s="46"/>
+      <c r="R227" s="46"/>
+      <c r="S227" s="46"/>
+      <c r="T227" s="46"/>
+      <c r="U227" s="46"/>
+      <c r="V227" s="46"/>
+      <c r="W227" s="46"/>
+      <c r="X227" s="46"/>
+      <c r="Y227" s="46"/>
+      <c r="Z227" s="46"/>
+      <c r="AA227" s="46"/>
+      <c r="AB227" s="46"/>
+      <c r="AC227" s="46"/>
+      <c r="AD227" s="46"/>
+      <c r="AE227" s="46"/>
+      <c r="AF227" s="46"/>
+      <c r="AG227" s="46"/>
+      <c r="AH227" s="46"/>
+      <c r="AI227" s="46"/>
+      <c r="AJ227" s="46"/>
+      <c r="AK227" s="47"/>
     </row>
     <row r="228" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
@@ -20808,7 +20733,7 @@
       <c r="L229" s="1">
         <v>1</v>
       </c>
-      <c r="M229" s="41" t="s">
+      <c r="M229" s="38" t="s">
         <v>591</v>
       </c>
       <c r="N229" s="1"/>
@@ -20865,7 +20790,7 @@
       <c r="L230" s="1">
         <v>1</v>
       </c>
-      <c r="M230" s="41"/>
+      <c r="M230" s="38"/>
       <c r="N230" s="1"/>
       <c r="O230" s="1"/>
       <c r="P230" s="1"/>
@@ -21236,54 +21161,54 @@
       <c r="AK236" s="1"/>
     </row>
     <row r="237" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A237" s="69" t="s">
+      <c r="A237" s="45" t="s">
         <v>638</v>
       </c>
-      <c r="B237" s="70"/>
-      <c r="C237" s="70"/>
-      <c r="D237" s="70"/>
-      <c r="E237" s="70"/>
-      <c r="F237" s="70"/>
-      <c r="G237" s="70"/>
-      <c r="H237" s="70"/>
-      <c r="I237" s="70"/>
-      <c r="J237" s="70"/>
-      <c r="K237" s="70"/>
-      <c r="L237" s="70"/>
-      <c r="M237" s="70"/>
-      <c r="N237" s="70"/>
-      <c r="O237" s="70"/>
-      <c r="P237" s="70"/>
-      <c r="Q237" s="70"/>
-      <c r="R237" s="70"/>
-      <c r="S237" s="70"/>
-      <c r="T237" s="70"/>
-      <c r="U237" s="70"/>
-      <c r="V237" s="70"/>
-      <c r="W237" s="70"/>
-      <c r="X237" s="70"/>
-      <c r="Y237" s="70"/>
-      <c r="Z237" s="70"/>
-      <c r="AA237" s="70"/>
-      <c r="AB237" s="70"/>
-      <c r="AC237" s="70"/>
-      <c r="AD237" s="70"/>
-      <c r="AE237" s="70"/>
-      <c r="AF237" s="70"/>
-      <c r="AG237" s="70"/>
-      <c r="AH237" s="70"/>
-      <c r="AI237" s="70"/>
-      <c r="AJ237" s="70"/>
-      <c r="AK237" s="71"/>
+      <c r="B237" s="46"/>
+      <c r="C237" s="46"/>
+      <c r="D237" s="46"/>
+      <c r="E237" s="46"/>
+      <c r="F237" s="46"/>
+      <c r="G237" s="46"/>
+      <c r="H237" s="46"/>
+      <c r="I237" s="46"/>
+      <c r="J237" s="46"/>
+      <c r="K237" s="46"/>
+      <c r="L237" s="46"/>
+      <c r="M237" s="46"/>
+      <c r="N237" s="46"/>
+      <c r="O237" s="46"/>
+      <c r="P237" s="46"/>
+      <c r="Q237" s="46"/>
+      <c r="R237" s="46"/>
+      <c r="S237" s="46"/>
+      <c r="T237" s="46"/>
+      <c r="U237" s="46"/>
+      <c r="V237" s="46"/>
+      <c r="W237" s="46"/>
+      <c r="X237" s="46"/>
+      <c r="Y237" s="46"/>
+      <c r="Z237" s="46"/>
+      <c r="AA237" s="46"/>
+      <c r="AB237" s="46"/>
+      <c r="AC237" s="46"/>
+      <c r="AD237" s="46"/>
+      <c r="AE237" s="46"/>
+      <c r="AF237" s="46"/>
+      <c r="AG237" s="46"/>
+      <c r="AH237" s="46"/>
+      <c r="AI237" s="46"/>
+      <c r="AJ237" s="46"/>
+      <c r="AK237" s="47"/>
     </row>
     <row r="238" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A238" s="37" t="s">
+      <c r="A238" s="2" t="s">
         <v>643</v>
       </c>
       <c r="B238" s="26" t="s">
         <v>629</v>
       </c>
-      <c r="C238" s="50" t="s">
+      <c r="C238" s="42" t="s">
         <v>625</v>
       </c>
       <c r="D238" s="3"/>
@@ -21301,7 +21226,7 @@
       <c r="J238" s="1"/>
       <c r="K238" s="1"/>
       <c r="L238" s="1"/>
-      <c r="M238" s="37" t="s">
+      <c r="M238" s="2" t="s">
         <v>635</v>
       </c>
       <c r="N238" s="1"/>
@@ -21322,7 +21247,7 @@
         <v>42</v>
       </c>
       <c r="AA238" s="1"/>
-      <c r="AB238" s="37">
+      <c r="AB238" s="2">
         <v>1</v>
       </c>
       <c r="AC238" s="1"/>
@@ -21340,13 +21265,13 @@
       <c r="AK238" s="1"/>
     </row>
     <row r="239" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A239" s="37" t="s">
+      <c r="A239" s="2" t="s">
         <v>643</v>
       </c>
       <c r="B239" s="26" t="s">
         <v>630</v>
       </c>
-      <c r="C239" s="50" t="s">
+      <c r="C239" s="42" t="s">
         <v>626</v>
       </c>
       <c r="D239" s="3"/>
@@ -21362,7 +21287,7 @@
       <c r="J239" s="2"/>
       <c r="K239" s="2"/>
       <c r="L239" s="2"/>
-      <c r="M239" s="37" t="s">
+      <c r="M239" s="2" t="s">
         <v>636</v>
       </c>
       <c r="N239" s="2"/>
@@ -21399,13 +21324,13 @@
       <c r="AK239" s="1"/>
     </row>
     <row r="240" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A240" s="37" t="s">
+      <c r="A240" s="2" t="s">
         <v>643</v>
       </c>
       <c r="B240" s="26" t="s">
         <v>631</v>
       </c>
-      <c r="C240" s="50" t="s">
+      <c r="C240" s="42" t="s">
         <v>627</v>
       </c>
       <c r="D240" s="3"/>
@@ -21421,7 +21346,7 @@
       <c r="J240" s="2"/>
       <c r="K240" s="2"/>
       <c r="L240" s="2"/>
-      <c r="M240" s="37" t="s">
+      <c r="M240" s="2" t="s">
         <v>637</v>
       </c>
       <c r="N240" s="2"/>
@@ -21458,13 +21383,13 @@
       <c r="AK240" s="1"/>
     </row>
     <row r="241" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A241" s="37" t="s">
+      <c r="A241" s="2" t="s">
         <v>643</v>
       </c>
       <c r="B241" s="26" t="s">
         <v>632</v>
       </c>
-      <c r="C241" s="50" t="s">
+      <c r="C241" s="42" t="s">
         <v>628</v>
       </c>
       <c r="D241" s="3"/>
@@ -21511,13 +21436,13 @@
       <c r="AK241" s="1"/>
     </row>
     <row r="242" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A242" s="37" t="s">
+      <c r="A242" s="2" t="s">
         <v>643</v>
       </c>
       <c r="B242" s="26" t="s">
         <v>633</v>
       </c>
-      <c r="C242" s="50" t="s">
+      <c r="C242" s="42" t="s">
         <v>97</v>
       </c>
       <c r="D242" s="3"/>
@@ -21568,45 +21493,45 @@
       <c r="AK242" s="1"/>
     </row>
     <row r="243" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A243" s="69" t="s">
+      <c r="A243" s="45" t="s">
         <v>697</v>
       </c>
-      <c r="B243" s="70"/>
-      <c r="C243" s="70"/>
-      <c r="D243" s="70"/>
-      <c r="E243" s="70"/>
-      <c r="F243" s="70"/>
-      <c r="G243" s="70"/>
-      <c r="H243" s="70"/>
-      <c r="I243" s="70"/>
-      <c r="J243" s="70"/>
-      <c r="K243" s="70"/>
-      <c r="L243" s="70"/>
-      <c r="M243" s="70"/>
-      <c r="N243" s="70"/>
-      <c r="O243" s="70"/>
-      <c r="P243" s="70"/>
-      <c r="Q243" s="70"/>
-      <c r="R243" s="70"/>
-      <c r="S243" s="70"/>
-      <c r="T243" s="70"/>
-      <c r="U243" s="70"/>
-      <c r="V243" s="70"/>
-      <c r="W243" s="70"/>
-      <c r="X243" s="70"/>
-      <c r="Y243" s="70"/>
-      <c r="Z243" s="70"/>
-      <c r="AA243" s="70"/>
-      <c r="AB243" s="70"/>
-      <c r="AC243" s="70"/>
-      <c r="AD243" s="70"/>
-      <c r="AE243" s="70"/>
-      <c r="AF243" s="70"/>
-      <c r="AG243" s="70"/>
-      <c r="AH243" s="70"/>
-      <c r="AI243" s="70"/>
-      <c r="AJ243" s="70"/>
-      <c r="AK243" s="71"/>
+      <c r="B243" s="46"/>
+      <c r="C243" s="46"/>
+      <c r="D243" s="46"/>
+      <c r="E243" s="46"/>
+      <c r="F243" s="46"/>
+      <c r="G243" s="46"/>
+      <c r="H243" s="46"/>
+      <c r="I243" s="46"/>
+      <c r="J243" s="46"/>
+      <c r="K243" s="46"/>
+      <c r="L243" s="46"/>
+      <c r="M243" s="46"/>
+      <c r="N243" s="46"/>
+      <c r="O243" s="46"/>
+      <c r="P243" s="46"/>
+      <c r="Q243" s="46"/>
+      <c r="R243" s="46"/>
+      <c r="S243" s="46"/>
+      <c r="T243" s="46"/>
+      <c r="U243" s="46"/>
+      <c r="V243" s="46"/>
+      <c r="W243" s="46"/>
+      <c r="X243" s="46"/>
+      <c r="Y243" s="46"/>
+      <c r="Z243" s="46"/>
+      <c r="AA243" s="46"/>
+      <c r="AB243" s="46"/>
+      <c r="AC243" s="46"/>
+      <c r="AD243" s="46"/>
+      <c r="AE243" s="46"/>
+      <c r="AF243" s="46"/>
+      <c r="AG243" s="46"/>
+      <c r="AH243" s="46"/>
+      <c r="AI243" s="46"/>
+      <c r="AJ243" s="46"/>
+      <c r="AK243" s="47"/>
     </row>
     <row r="244" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A244" s="26" t="s">
@@ -21806,7 +21731,7 @@
       <c r="J247" s="2"/>
       <c r="K247" s="2"/>
       <c r="L247" s="2"/>
-      <c r="M247" s="37" t="s">
+      <c r="M247" s="2" t="s">
         <v>661</v>
       </c>
       <c r="N247" s="2"/>
@@ -21898,59 +21823,59 @@
       <c r="AK248" s="1"/>
     </row>
     <row r="249" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A249" s="69" t="s">
+      <c r="A249" s="45" t="s">
         <v>696</v>
       </c>
-      <c r="B249" s="70"/>
-      <c r="C249" s="70"/>
-      <c r="D249" s="70"/>
-      <c r="E249" s="70"/>
-      <c r="F249" s="70"/>
-      <c r="G249" s="70"/>
-      <c r="H249" s="70"/>
-      <c r="I249" s="70"/>
-      <c r="J249" s="70"/>
-      <c r="K249" s="70"/>
-      <c r="L249" s="70"/>
-      <c r="M249" s="70"/>
-      <c r="N249" s="70"/>
-      <c r="O249" s="70"/>
-      <c r="P249" s="70"/>
-      <c r="Q249" s="70"/>
-      <c r="R249" s="70"/>
-      <c r="S249" s="70"/>
-      <c r="T249" s="70"/>
-      <c r="U249" s="70"/>
-      <c r="V249" s="70"/>
-      <c r="W249" s="70"/>
-      <c r="X249" s="70"/>
-      <c r="Y249" s="70"/>
-      <c r="Z249" s="70"/>
-      <c r="AA249" s="70"/>
-      <c r="AB249" s="70"/>
-      <c r="AC249" s="70"/>
-      <c r="AD249" s="70"/>
-      <c r="AE249" s="70"/>
-      <c r="AF249" s="70"/>
-      <c r="AG249" s="70"/>
-      <c r="AH249" s="70"/>
-      <c r="AI249" s="70"/>
-      <c r="AJ249" s="70"/>
-      <c r="AK249" s="71"/>
+      <c r="B249" s="46"/>
+      <c r="C249" s="46"/>
+      <c r="D249" s="46"/>
+      <c r="E249" s="46"/>
+      <c r="F249" s="46"/>
+      <c r="G249" s="46"/>
+      <c r="H249" s="46"/>
+      <c r="I249" s="46"/>
+      <c r="J249" s="46"/>
+      <c r="K249" s="46"/>
+      <c r="L249" s="46"/>
+      <c r="M249" s="46"/>
+      <c r="N249" s="46"/>
+      <c r="O249" s="46"/>
+      <c r="P249" s="46"/>
+      <c r="Q249" s="46"/>
+      <c r="R249" s="46"/>
+      <c r="S249" s="46"/>
+      <c r="T249" s="46"/>
+      <c r="U249" s="46"/>
+      <c r="V249" s="46"/>
+      <c r="W249" s="46"/>
+      <c r="X249" s="46"/>
+      <c r="Y249" s="46"/>
+      <c r="Z249" s="46"/>
+      <c r="AA249" s="46"/>
+      <c r="AB249" s="46"/>
+      <c r="AC249" s="46"/>
+      <c r="AD249" s="46"/>
+      <c r="AE249" s="46"/>
+      <c r="AF249" s="46"/>
+      <c r="AG249" s="46"/>
+      <c r="AH249" s="46"/>
+      <c r="AI249" s="46"/>
+      <c r="AJ249" s="46"/>
+      <c r="AK249" s="47"/>
     </row>
     <row r="250" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A250" s="62" t="s">
+      <c r="A250" s="26" t="s">
         <v>691</v>
       </c>
-      <c r="B250" s="62" t="s">
+      <c r="B250" s="26" t="s">
         <v>682</v>
       </c>
-      <c r="C250" s="62" t="s">
+      <c r="C250" s="26" t="s">
         <v>685</v>
       </c>
-      <c r="D250" s="3"/>
-      <c r="E250" s="3"/>
-      <c r="F250" s="37">
+      <c r="D250" s="7"/>
+      <c r="E250" s="7"/>
+      <c r="F250" s="2">
         <v>1</v>
       </c>
       <c r="G250" s="4">
@@ -21998,18 +21923,18 @@
       <c r="AK250" s="1"/>
     </row>
     <row r="251" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A251" s="62" t="s">
+      <c r="A251" s="26" t="s">
         <v>691</v>
       </c>
-      <c r="B251" s="62" t="s">
+      <c r="B251" s="26" t="s">
         <v>683</v>
       </c>
-      <c r="C251" s="62" t="s">
+      <c r="C251" s="26" t="s">
         <v>686</v>
       </c>
-      <c r="D251" s="3"/>
-      <c r="E251" s="3"/>
-      <c r="F251" s="37">
+      <c r="D251" s="7"/>
+      <c r="E251" s="7"/>
+      <c r="F251" s="2">
         <v>1</v>
       </c>
       <c r="G251" s="8"/>
@@ -22057,18 +21982,18 @@
       <c r="AK251" s="1"/>
     </row>
     <row r="252" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A252" s="62" t="s">
+      <c r="A252" s="26" t="s">
         <v>691</v>
       </c>
-      <c r="B252" s="62" t="s">
+      <c r="B252" s="26" t="s">
         <v>684</v>
       </c>
-      <c r="C252" s="62" t="s">
+      <c r="C252" s="26" t="s">
         <v>687</v>
       </c>
-      <c r="D252" s="3"/>
-      <c r="E252" s="3"/>
-      <c r="F252" s="37">
+      <c r="D252" s="7"/>
+      <c r="E252" s="7"/>
+      <c r="F252" s="2">
         <v>1</v>
       </c>
       <c r="G252" s="8"/>
@@ -22079,7 +22004,7 @@
       <c r="J252" s="2"/>
       <c r="K252" s="2"/>
       <c r="L252" s="2"/>
-      <c r="M252" s="37" t="s">
+      <c r="M252" s="2" t="s">
         <v>661</v>
       </c>
       <c r="N252" s="2"/>
@@ -22114,59 +22039,59 @@
       <c r="AK252" s="1"/>
     </row>
     <row r="253" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A253" s="69" t="s">
+      <c r="A253" s="45" t="s">
         <v>694</v>
       </c>
-      <c r="B253" s="70"/>
-      <c r="C253" s="70"/>
-      <c r="D253" s="70"/>
-      <c r="E253" s="70"/>
-      <c r="F253" s="70"/>
-      <c r="G253" s="70"/>
-      <c r="H253" s="70"/>
-      <c r="I253" s="70"/>
-      <c r="J253" s="70"/>
-      <c r="K253" s="70"/>
-      <c r="L253" s="70"/>
-      <c r="M253" s="70"/>
-      <c r="N253" s="70"/>
-      <c r="O253" s="70"/>
-      <c r="P253" s="70"/>
-      <c r="Q253" s="70"/>
-      <c r="R253" s="70"/>
-      <c r="S253" s="70"/>
-      <c r="T253" s="70"/>
-      <c r="U253" s="70"/>
-      <c r="V253" s="70"/>
-      <c r="W253" s="70"/>
-      <c r="X253" s="70"/>
-      <c r="Y253" s="70"/>
-      <c r="Z253" s="70"/>
-      <c r="AA253" s="70"/>
-      <c r="AB253" s="70"/>
-      <c r="AC253" s="70"/>
-      <c r="AD253" s="70"/>
-      <c r="AE253" s="70"/>
-      <c r="AF253" s="70"/>
-      <c r="AG253" s="70"/>
-      <c r="AH253" s="70"/>
-      <c r="AI253" s="70"/>
-      <c r="AJ253" s="70"/>
-      <c r="AK253" s="71"/>
+      <c r="B253" s="46"/>
+      <c r="C253" s="46"/>
+      <c r="D253" s="46"/>
+      <c r="E253" s="46"/>
+      <c r="F253" s="46"/>
+      <c r="G253" s="46"/>
+      <c r="H253" s="46"/>
+      <c r="I253" s="46"/>
+      <c r="J253" s="46"/>
+      <c r="K253" s="46"/>
+      <c r="L253" s="46"/>
+      <c r="M253" s="46"/>
+      <c r="N253" s="46"/>
+      <c r="O253" s="46"/>
+      <c r="P253" s="46"/>
+      <c r="Q253" s="46"/>
+      <c r="R253" s="46"/>
+      <c r="S253" s="46"/>
+      <c r="T253" s="46"/>
+      <c r="U253" s="46"/>
+      <c r="V253" s="46"/>
+      <c r="W253" s="46"/>
+      <c r="X253" s="46"/>
+      <c r="Y253" s="46"/>
+      <c r="Z253" s="46"/>
+      <c r="AA253" s="46"/>
+      <c r="AB253" s="46"/>
+      <c r="AC253" s="46"/>
+      <c r="AD253" s="46"/>
+      <c r="AE253" s="46"/>
+      <c r="AF253" s="46"/>
+      <c r="AG253" s="46"/>
+      <c r="AH253" s="46"/>
+      <c r="AI253" s="46"/>
+      <c r="AJ253" s="46"/>
+      <c r="AK253" s="47"/>
     </row>
     <row r="254" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A254" s="37" t="s">
+      <c r="A254" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="B254" s="62" t="s">
+      <c r="B254" s="26" t="s">
         <v>479</v>
       </c>
-      <c r="C254" s="62" t="s">
+      <c r="C254" s="26" t="s">
         <v>454</v>
       </c>
-      <c r="D254" s="3"/>
-      <c r="E254" s="3"/>
-      <c r="F254" s="37">
+      <c r="D254" s="7"/>
+      <c r="E254" s="7"/>
+      <c r="F254" s="2">
         <v>1</v>
       </c>
       <c r="G254" s="4">
@@ -22208,18 +22133,18 @@
       <c r="AK254" s="1"/>
     </row>
     <row r="255" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A255" s="37" t="s">
+      <c r="A255" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="B255" s="62" t="s">
+      <c r="B255" s="26" t="s">
         <v>488</v>
       </c>
-      <c r="C255" s="62" t="s">
+      <c r="C255" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="D255" s="3"/>
-      <c r="E255" s="3"/>
-      <c r="F255" s="37">
+      <c r="D255" s="7"/>
+      <c r="E255" s="7"/>
+      <c r="F255" s="2">
         <v>1</v>
       </c>
       <c r="G255" s="8"/>
@@ -22259,18 +22184,18 @@
       <c r="AK255" s="1"/>
     </row>
     <row r="256" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A256" s="37" t="s">
+      <c r="A256" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="B256" s="62" t="s">
+      <c r="B256" s="26" t="s">
         <v>682</v>
       </c>
-      <c r="C256" s="62" t="s">
+      <c r="C256" s="26" t="s">
         <v>685</v>
       </c>
-      <c r="D256" s="3"/>
-      <c r="E256" s="3"/>
-      <c r="F256" s="37">
+      <c r="D256" s="7"/>
+      <c r="E256" s="7"/>
+      <c r="F256" s="2">
         <v>1</v>
       </c>
       <c r="G256" s="4"/>
@@ -22312,16 +22237,6 @@
   </sheetData>
   <autoFilter ref="A1:AJ256" xr:uid="{0580B1DF-60C2-4E2B-940A-667729080FCF}"/>
   <mergeCells count="17">
-    <mergeCell ref="A186:AK186"/>
-    <mergeCell ref="A178:AK178"/>
-    <mergeCell ref="A169:AK169"/>
-    <mergeCell ref="A2:AK2"/>
-    <mergeCell ref="A60:AK60"/>
-    <mergeCell ref="A253:AK253"/>
-    <mergeCell ref="A249:AK249"/>
-    <mergeCell ref="A243:AK243"/>
-    <mergeCell ref="A237:AK237"/>
-    <mergeCell ref="A227:AK227"/>
     <mergeCell ref="A215:AK215"/>
     <mergeCell ref="A163:AK163"/>
     <mergeCell ref="A158:AK158"/>
@@ -22329,6 +22244,16 @@
     <mergeCell ref="A129:AK129"/>
     <mergeCell ref="A208:AK208"/>
     <mergeCell ref="A201:AK201"/>
+    <mergeCell ref="A253:AK253"/>
+    <mergeCell ref="A249:AK249"/>
+    <mergeCell ref="A243:AK243"/>
+    <mergeCell ref="A237:AK237"/>
+    <mergeCell ref="A227:AK227"/>
+    <mergeCell ref="A186:AK186"/>
+    <mergeCell ref="A178:AK178"/>
+    <mergeCell ref="A169:AK169"/>
+    <mergeCell ref="A2:AK2"/>
+    <mergeCell ref="A60:AK60"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22418,7 +22343,7 @@
         <v>409</v>
       </c>
       <c r="F2" s="29"/>
-      <c r="G2" s="44" t="s">
+      <c r="G2" s="40" t="s">
         <v>298</v>
       </c>
       <c r="H2" s="29">
@@ -22527,10 +22452,10 @@
       <c r="B5" s="29">
         <v>1020</v>
       </c>
-      <c r="C5" s="45" t="s">
+      <c r="C5" s="41" t="s">
         <v>606</v>
       </c>
-      <c r="D5" s="43" t="s">
+      <c r="D5" s="39" t="s">
         <v>596</v>
       </c>
       <c r="E5" s="29"/>
@@ -22558,10 +22483,10 @@
       <c r="B6" s="29">
         <v>1020</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="C6" s="41" t="s">
         <v>607</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="39" t="s">
         <v>597</v>
       </c>
       <c r="E6" s="29"/>
@@ -22589,10 +22514,10 @@
       <c r="B7" s="29">
         <v>1020</v>
       </c>
-      <c r="C7" s="45" t="s">
+      <c r="C7" s="41" t="s">
         <v>608</v>
       </c>
-      <c r="D7" s="43" t="s">
+      <c r="D7" s="39" t="s">
         <v>598</v>
       </c>
       <c r="E7" s="29"/>
@@ -22620,10 +22545,10 @@
       <c r="B8" s="29">
         <v>1020</v>
       </c>
-      <c r="C8" s="45" t="s">
+      <c r="C8" s="41" t="s">
         <v>612</v>
       </c>
-      <c r="D8" s="43" t="s">
+      <c r="D8" s="39" t="s">
         <v>599</v>
       </c>
       <c r="E8" s="29"/>
@@ -22651,10 +22576,10 @@
       <c r="B9" s="29">
         <v>1020</v>
       </c>
-      <c r="C9" s="45" t="s">
+      <c r="C9" s="41" t="s">
         <v>613</v>
       </c>
-      <c r="D9" s="43" t="s">
+      <c r="D9" s="39" t="s">
         <v>600</v>
       </c>
       <c r="E9" s="29"/>
@@ -22682,10 +22607,10 @@
       <c r="B10" s="29">
         <v>1020</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="41" t="s">
         <v>614</v>
       </c>
-      <c r="D10" s="43" t="s">
+      <c r="D10" s="39" t="s">
         <v>601</v>
       </c>
       <c r="E10" s="29"/>
@@ -22713,10 +22638,10 @@
       <c r="B11" s="29">
         <v>1020</v>
       </c>
-      <c r="C11" s="45" t="s">
+      <c r="C11" s="41" t="s">
         <v>615</v>
       </c>
-      <c r="D11" s="43" t="s">
+      <c r="D11" s="39" t="s">
         <v>602</v>
       </c>
       <c r="E11" s="29"/>
@@ -22744,10 +22669,10 @@
       <c r="B12" s="29">
         <v>1020</v>
       </c>
-      <c r="C12" s="45" t="s">
+      <c r="C12" s="41" t="s">
         <v>616</v>
       </c>
-      <c r="D12" s="43" t="s">
+      <c r="D12" s="39" t="s">
         <v>603</v>
       </c>
       <c r="E12" s="29"/>
@@ -22775,10 +22700,10 @@
       <c r="B13" s="29">
         <v>1020</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="41" t="s">
         <v>617</v>
       </c>
-      <c r="D13" s="43" t="s">
+      <c r="D13" s="39" t="s">
         <v>604</v>
       </c>
       <c r="E13" s="29"/>
@@ -22806,10 +22731,10 @@
       <c r="B14" s="29">
         <v>1020</v>
       </c>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="41" t="s">
         <v>618</v>
       </c>
-      <c r="D14" s="43" t="s">
+      <c r="D14" s="39" t="s">
         <v>605</v>
       </c>
       <c r="E14" s="29"/>
@@ -22922,106 +22847,106 @@
       <c r="E17" s="29" t="s">
         <v>515</v>
       </c>
-      <c r="F17" s="30"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="30">
+      <c r="F17" s="29"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="29">
         <v>0</v>
       </c>
-      <c r="I17" s="31"/>
+      <c r="I17" s="40"/>
       <c r="J17" s="7" t="s">
         <v>419</v>
       </c>
-      <c r="K17" s="30">
-        <v>1</v>
-      </c>
-      <c r="L17" s="30">
+      <c r="K17" s="29">
+        <v>1</v>
+      </c>
+      <c r="L17" s="29">
         <v>0</v>
       </c>
-      <c r="M17" s="30">
+      <c r="M17" s="29">
         <v>1</v>
       </c>
       <c r="N17" s="29">
         <v>1050</v>
       </c>
-      <c r="O17" s="30" t="s">
+      <c r="O17" s="29" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A18" s="49">
+      <c r="A18" s="29">
         <v>1060</v>
       </c>
-      <c r="B18" s="49">
+      <c r="B18" s="29">
         <v>10</v>
       </c>
-      <c r="C18" s="49"/>
-      <c r="D18" s="49" t="s">
+      <c r="C18" s="29"/>
+      <c r="D18" s="29" t="s">
         <v>639</v>
       </c>
-      <c r="E18" s="47" t="s">
+      <c r="E18" s="29" t="s">
         <v>640</v>
       </c>
-      <c r="F18" s="49"/>
-      <c r="G18" s="48"/>
-      <c r="H18" s="49">
+      <c r="F18" s="29"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="29">
         <v>0</v>
       </c>
-      <c r="I18" s="48"/>
-      <c r="J18" s="52" t="s">
+      <c r="I18" s="40"/>
+      <c r="J18" s="51" t="s">
         <v>641</v>
       </c>
-      <c r="K18" s="49">
-        <v>1</v>
-      </c>
-      <c r="L18" s="49">
+      <c r="K18" s="29">
+        <v>1</v>
+      </c>
+      <c r="L18" s="29">
         <v>0</v>
       </c>
-      <c r="M18" s="30">
-        <v>1</v>
-      </c>
-      <c r="N18" s="49">
+      <c r="M18" s="29">
+        <v>1</v>
+      </c>
+      <c r="N18" s="29">
         <v>1060</v>
       </c>
-      <c r="O18" s="49" t="s">
+      <c r="O18" s="29" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A19" s="49">
+      <c r="A19" s="29">
         <v>1070</v>
       </c>
-      <c r="B19" s="49">
+      <c r="B19" s="29">
         <v>10</v>
       </c>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49" t="s">
+      <c r="C19" s="29"/>
+      <c r="D19" s="29" t="s">
         <v>621</v>
       </c>
-      <c r="E19" s="47" t="s">
+      <c r="E19" s="29" t="s">
         <v>622</v>
       </c>
-      <c r="F19" s="49"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="49">
+      <c r="F19" s="29"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="29">
         <v>0</v>
       </c>
-      <c r="I19" s="49"/>
-      <c r="J19" s="52" t="s">
+      <c r="I19" s="29"/>
+      <c r="J19" s="51" t="s">
         <v>642</v>
       </c>
-      <c r="K19" s="49">
-        <v>1</v>
-      </c>
-      <c r="L19" s="49">
+      <c r="K19" s="29">
+        <v>1</v>
+      </c>
+      <c r="L19" s="29">
         <v>0</v>
       </c>
-      <c r="M19" s="30">
-        <v>1</v>
-      </c>
-      <c r="N19" s="49">
+      <c r="M19" s="29">
+        <v>1</v>
+      </c>
+      <c r="N19" s="29">
         <v>1070</v>
       </c>
-      <c r="O19" s="49" t="s">
+      <c r="O19" s="29" t="s">
         <v>422</v>
       </c>
     </row>
@@ -23040,11 +22965,11 @@
         <v>738</v>
       </c>
       <c r="F20" s="29"/>
-      <c r="G20" s="44"/>
+      <c r="G20" s="40"/>
       <c r="H20" s="29">
         <v>0</v>
       </c>
-      <c r="I20" s="44"/>
+      <c r="I20" s="40"/>
       <c r="J20" s="7" t="s">
         <v>419</v>
       </c>
@@ -23054,7 +22979,7 @@
       <c r="L20" s="29">
         <v>0</v>
       </c>
-      <c r="M20" s="30">
+      <c r="M20" s="29">
         <v>1</v>
       </c>
       <c r="N20" s="29">
@@ -23079,11 +23004,11 @@
         <v>739</v>
       </c>
       <c r="F21" s="29"/>
-      <c r="G21" s="44"/>
+      <c r="G21" s="40"/>
       <c r="H21" s="29">
         <v>0</v>
       </c>
-      <c r="I21" s="44"/>
+      <c r="I21" s="40"/>
       <c r="J21" s="7" t="s">
         <v>419</v>
       </c>
@@ -23093,7 +23018,7 @@
       <c r="L21" s="29">
         <v>0</v>
       </c>
-      <c r="M21" s="30">
+      <c r="M21" s="29">
         <v>1</v>
       </c>
       <c r="N21" s="29">
@@ -23118,12 +23043,12 @@
         <v>701</v>
       </c>
       <c r="F22" s="29"/>
-      <c r="G22" s="44"/>
+      <c r="G22" s="40"/>
       <c r="H22" s="29">
         <v>0</v>
       </c>
       <c r="I22" s="29"/>
-      <c r="J22" s="67" t="s">
+      <c r="J22" s="29" t="s">
         <v>715</v>
       </c>
       <c r="K22" s="29">
@@ -23132,13 +23057,13 @@
       <c r="L22" s="29">
         <v>0</v>
       </c>
-      <c r="M22" s="30">
+      <c r="M22" s="29">
         <v>1</v>
       </c>
       <c r="N22" s="29">
         <v>1100</v>
       </c>
-      <c r="O22" s="30" t="s">
+      <c r="O22" s="29" t="s">
         <v>422</v>
       </c>
     </row>
@@ -23157,7 +23082,7 @@
         <v>675</v>
       </c>
       <c r="F23" s="29"/>
-      <c r="G23" s="44"/>
+      <c r="G23" s="40"/>
       <c r="H23" s="29">
         <v>0</v>
       </c>
@@ -23171,13 +23096,13 @@
       <c r="L23" s="29">
         <v>0</v>
       </c>
-      <c r="M23" s="30">
+      <c r="M23" s="29">
         <v>1</v>
       </c>
       <c r="N23" s="29">
         <v>1110</v>
       </c>
-      <c r="O23" s="30" t="s">
+      <c r="O23" s="29" t="s">
         <v>422</v>
       </c>
     </row>
@@ -23196,7 +23121,7 @@
         <v>693</v>
       </c>
       <c r="F24" s="29"/>
-      <c r="G24" s="44"/>
+      <c r="G24" s="40"/>
       <c r="H24" s="29">
         <v>0</v>
       </c>
@@ -23233,7 +23158,7 @@
         <v>415</v>
       </c>
       <c r="F25" s="29"/>
-      <c r="G25" s="44" t="s">
+      <c r="G25" s="40" t="s">
         <v>298</v>
       </c>
       <c r="H25" s="29">
@@ -23272,11 +23197,11 @@
         <v>442</v>
       </c>
       <c r="F26" s="29"/>
-      <c r="G26" s="44"/>
+      <c r="G26" s="40"/>
       <c r="H26" s="29">
         <v>0</v>
       </c>
-      <c r="I26" s="44"/>
+      <c r="I26" s="40"/>
       <c r="J26" s="7" t="s">
         <v>419</v>
       </c>
@@ -23311,11 +23236,11 @@
         <v>443</v>
       </c>
       <c r="F27" s="29"/>
-      <c r="G27" s="44"/>
+      <c r="G27" s="40"/>
       <c r="H27" s="29">
         <v>0</v>
       </c>
-      <c r="I27" s="44"/>
+      <c r="I27" s="40"/>
       <c r="J27" s="7" t="s">
         <v>419</v>
       </c>
@@ -23350,11 +23275,11 @@
         <v>444</v>
       </c>
       <c r="F28" s="29"/>
-      <c r="G28" s="44"/>
+      <c r="G28" s="40"/>
       <c r="H28" s="29">
         <v>0</v>
       </c>
-      <c r="I28" s="44"/>
+      <c r="I28" s="40"/>
       <c r="J28" s="36" t="s">
         <v>742</v>
       </c>
@@ -23472,7 +23397,7 @@
       <c r="G1" s="23" t="s">
         <v>566</v>
       </c>
-      <c r="H1" s="55" t="s">
+      <c r="H1" s="23" t="s">
         <v>650</v>
       </c>
       <c r="I1" s="23" t="s">
@@ -23505,7 +23430,7 @@
       <c r="H2" s="53" t="s">
         <v>648</v>
       </c>
-      <c r="I2" s="54"/>
+      <c r="I2" s="55"/>
       <c r="J2" s="53" t="s">
         <v>649</v>
       </c>
@@ -23514,25 +23439,25 @@
       <c r="A3" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="53" t="s">
         <v>656</v>
       </c>
-      <c r="C3" s="41"/>
+      <c r="C3" s="53"/>
       <c r="D3" s="26" t="s">
         <v>582</v>
       </c>
       <c r="E3" s="26" t="s">
         <v>655</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="53" t="s">
         <v>568</v>
       </c>
-      <c r="G3" s="41" t="s">
+      <c r="G3" s="53" t="s">
         <v>567</v>
       </c>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41" t="s">
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53" t="s">
         <v>654</v>
       </c>
     </row>
@@ -23540,17 +23465,17 @@
       <c r="A4" s="53" t="s">
         <v>657</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="53"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41" t="s">
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53" t="s">
         <v>659</v>
       </c>
-      <c r="J4" s="41" t="s">
+      <c r="J4" s="53" t="s">
         <v>658</v>
       </c>
     </row>

--- a/public/import_template/v0.2node/node_module.xlsx
+++ b/public/import_template/v0.2node/node_module.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\ddit\code\umi_max.260226_github\public\import_template\v0.2node\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0908BCD0-0D6F-41A6-AC17-9C2653A62522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18DC96FE-4A21-4321-B201-D19F6DB3822A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="762" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="762" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表" sheetId="8" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2334" uniqueCount="743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2342" uniqueCount="748">
   <si>
     <t>字段中文名</t>
   </si>
@@ -2729,6 +2729,26 @@
   </si>
   <si>
     <t>./easy_dev_dc/example/dict_module_media_ns</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>./common/automatic_page_enh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>进货明细E</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>/dynamicbs1/enh/cfgp/eg_m_mts_tsjh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>出口明细E</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>/dynamicbs1/enh/cfgp/eg_m_mts_tssb</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2852,7 +2872,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2952,6 +2972,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3068,7 +3094,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3190,6 +3216,26 @@
     <xf numFmtId="0" fontId="3" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3207,19 +3253,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -6656,7 +6689,7 @@
       <c r="C205" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="D205" s="52"/>
+      <c r="D205" s="46"/>
       <c r="E205" s="27"/>
       <c r="F205" s="27"/>
       <c r="G205" s="26"/>
@@ -6685,7 +6718,7 @@
       <c r="D207" s="26" t="s">
         <v>235</v>
       </c>
-      <c r="E207" s="52"/>
+      <c r="E207" s="46"/>
       <c r="F207" s="26" t="s">
         <v>236</v>
       </c>
@@ -6702,7 +6735,7 @@
         <v>455</v>
       </c>
       <c r="D208" s="26"/>
-      <c r="E208" s="52"/>
+      <c r="E208" s="46"/>
       <c r="F208" s="26"/>
       <c r="G208" s="26"/>
     </row>
@@ -6716,8 +6749,8 @@
       <c r="C209" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="D209" s="52"/>
-      <c r="E209" s="52"/>
+      <c r="D209" s="46"/>
+      <c r="E209" s="46"/>
       <c r="F209" s="27"/>
       <c r="G209" s="26"/>
     </row>
@@ -8070,45 +8103,45 @@
       </c>
     </row>
     <row r="2" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="53" t="s">
         <v>533</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="46"/>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="46"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46"/>
-      <c r="T2" s="46"/>
-      <c r="U2" s="46"/>
-      <c r="V2" s="46"/>
-      <c r="W2" s="46"/>
-      <c r="X2" s="46"/>
-      <c r="Y2" s="46"/>
-      <c r="Z2" s="46"/>
-      <c r="AA2" s="46"/>
-      <c r="AB2" s="46"/>
-      <c r="AC2" s="46"/>
-      <c r="AD2" s="46"/>
-      <c r="AE2" s="46"/>
-      <c r="AF2" s="46"/>
-      <c r="AG2" s="46"/>
-      <c r="AH2" s="46"/>
-      <c r="AI2" s="46"/>
-      <c r="AJ2" s="46"/>
-      <c r="AK2" s="47"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="54"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="54"/>
+      <c r="Q2" s="54"/>
+      <c r="R2" s="54"/>
+      <c r="S2" s="54"/>
+      <c r="T2" s="54"/>
+      <c r="U2" s="54"/>
+      <c r="V2" s="54"/>
+      <c r="W2" s="54"/>
+      <c r="X2" s="54"/>
+      <c r="Y2" s="54"/>
+      <c r="Z2" s="54"/>
+      <c r="AA2" s="54"/>
+      <c r="AB2" s="54"/>
+      <c r="AC2" s="54"/>
+      <c r="AD2" s="54"/>
+      <c r="AE2" s="54"/>
+      <c r="AF2" s="54"/>
+      <c r="AG2" s="54"/>
+      <c r="AH2" s="54"/>
+      <c r="AI2" s="54"/>
+      <c r="AJ2" s="54"/>
+      <c r="AK2" s="55"/>
     </row>
     <row r="3" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -8700,7 +8733,7 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
-      <c r="M12" s="52" t="s">
+      <c r="M12" s="46" t="s">
         <v>709</v>
       </c>
       <c r="N12" s="2"/>
@@ -8728,7 +8761,7 @@
       <c r="Z12" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AA12" s="52" t="s">
+      <c r="AA12" s="46" t="s">
         <v>709</v>
       </c>
       <c r="AB12" s="2"/>
@@ -9110,7 +9143,7 @@
         <v>85</v>
       </c>
       <c r="AB18" s="2"/>
-      <c r="AC18" s="52"/>
+      <c r="AC18" s="46"/>
       <c r="AD18" s="2"/>
       <c r="AE18" s="2"/>
       <c r="AF18" s="2"/>
@@ -9154,7 +9187,7 @@
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
-      <c r="P19" s="54" t="s">
+      <c r="P19" s="48" t="s">
         <v>710</v>
       </c>
       <c r="Q19" s="2"/>
@@ -9223,7 +9256,7 @@
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
-      <c r="P20" s="54" t="s">
+      <c r="P20" s="48" t="s">
         <v>711</v>
       </c>
       <c r="Q20" s="2"/>
@@ -9311,7 +9344,7 @@
         <v>80</v>
       </c>
       <c r="AB21" s="2"/>
-      <c r="AC21" s="52" t="s">
+      <c r="AC21" s="46" t="s">
         <v>714</v>
       </c>
       <c r="AD21" s="2"/>
@@ -11358,45 +11391,45 @@
       <c r="AK59" s="1"/>
     </row>
     <row r="60" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="45" t="s">
+      <c r="A60" s="53" t="s">
         <v>532</v>
       </c>
-      <c r="B60" s="46"/>
-      <c r="C60" s="46"/>
-      <c r="D60" s="46"/>
-      <c r="E60" s="46"/>
-      <c r="F60" s="46"/>
-      <c r="G60" s="46"/>
-      <c r="H60" s="46"/>
-      <c r="I60" s="46"/>
-      <c r="J60" s="46"/>
-      <c r="K60" s="46"/>
-      <c r="L60" s="46"/>
-      <c r="M60" s="46"/>
-      <c r="N60" s="46"/>
-      <c r="O60" s="46"/>
-      <c r="P60" s="46"/>
-      <c r="Q60" s="46"/>
-      <c r="R60" s="46"/>
-      <c r="S60" s="46"/>
-      <c r="T60" s="46"/>
-      <c r="U60" s="46"/>
-      <c r="V60" s="46"/>
-      <c r="W60" s="46"/>
-      <c r="X60" s="46"/>
-      <c r="Y60" s="46"/>
-      <c r="Z60" s="46"/>
-      <c r="AA60" s="46"/>
-      <c r="AB60" s="46"/>
-      <c r="AC60" s="46"/>
-      <c r="AD60" s="46"/>
-      <c r="AE60" s="46"/>
-      <c r="AF60" s="46"/>
-      <c r="AG60" s="46"/>
-      <c r="AH60" s="46"/>
-      <c r="AI60" s="46"/>
-      <c r="AJ60" s="46"/>
-      <c r="AK60" s="47"/>
+      <c r="B60" s="54"/>
+      <c r="C60" s="54"/>
+      <c r="D60" s="54"/>
+      <c r="E60" s="54"/>
+      <c r="F60" s="54"/>
+      <c r="G60" s="54"/>
+      <c r="H60" s="54"/>
+      <c r="I60" s="54"/>
+      <c r="J60" s="54"/>
+      <c r="K60" s="54"/>
+      <c r="L60" s="54"/>
+      <c r="M60" s="54"/>
+      <c r="N60" s="54"/>
+      <c r="O60" s="54"/>
+      <c r="P60" s="54"/>
+      <c r="Q60" s="54"/>
+      <c r="R60" s="54"/>
+      <c r="S60" s="54"/>
+      <c r="T60" s="54"/>
+      <c r="U60" s="54"/>
+      <c r="V60" s="54"/>
+      <c r="W60" s="54"/>
+      <c r="X60" s="54"/>
+      <c r="Y60" s="54"/>
+      <c r="Z60" s="54"/>
+      <c r="AA60" s="54"/>
+      <c r="AB60" s="54"/>
+      <c r="AC60" s="54"/>
+      <c r="AD60" s="54"/>
+      <c r="AE60" s="54"/>
+      <c r="AF60" s="54"/>
+      <c r="AG60" s="54"/>
+      <c r="AH60" s="54"/>
+      <c r="AI60" s="54"/>
+      <c r="AJ60" s="54"/>
+      <c r="AK60" s="55"/>
     </row>
     <row r="61" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
@@ -15201,45 +15234,45 @@
       <c r="AK128" s="1"/>
     </row>
     <row r="129" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="45" t="s">
+      <c r="A129" s="53" t="s">
         <v>531</v>
       </c>
-      <c r="B129" s="46"/>
-      <c r="C129" s="46"/>
-      <c r="D129" s="46"/>
-      <c r="E129" s="46"/>
-      <c r="F129" s="46"/>
-      <c r="G129" s="46"/>
-      <c r="H129" s="46"/>
-      <c r="I129" s="46"/>
-      <c r="J129" s="46"/>
-      <c r="K129" s="46"/>
-      <c r="L129" s="46"/>
-      <c r="M129" s="46"/>
-      <c r="N129" s="46"/>
-      <c r="O129" s="46"/>
-      <c r="P129" s="46"/>
-      <c r="Q129" s="46"/>
-      <c r="R129" s="46"/>
-      <c r="S129" s="46"/>
-      <c r="T129" s="46"/>
-      <c r="U129" s="46"/>
-      <c r="V129" s="46"/>
-      <c r="W129" s="46"/>
-      <c r="X129" s="46"/>
-      <c r="Y129" s="46"/>
-      <c r="Z129" s="46"/>
-      <c r="AA129" s="46"/>
-      <c r="AB129" s="46"/>
-      <c r="AC129" s="46"/>
-      <c r="AD129" s="46"/>
-      <c r="AE129" s="46"/>
-      <c r="AF129" s="46"/>
-      <c r="AG129" s="46"/>
-      <c r="AH129" s="46"/>
-      <c r="AI129" s="46"/>
-      <c r="AJ129" s="46"/>
-      <c r="AK129" s="47"/>
+      <c r="B129" s="54"/>
+      <c r="C129" s="54"/>
+      <c r="D129" s="54"/>
+      <c r="E129" s="54"/>
+      <c r="F129" s="54"/>
+      <c r="G129" s="54"/>
+      <c r="H129" s="54"/>
+      <c r="I129" s="54"/>
+      <c r="J129" s="54"/>
+      <c r="K129" s="54"/>
+      <c r="L129" s="54"/>
+      <c r="M129" s="54"/>
+      <c r="N129" s="54"/>
+      <c r="O129" s="54"/>
+      <c r="P129" s="54"/>
+      <c r="Q129" s="54"/>
+      <c r="R129" s="54"/>
+      <c r="S129" s="54"/>
+      <c r="T129" s="54"/>
+      <c r="U129" s="54"/>
+      <c r="V129" s="54"/>
+      <c r="W129" s="54"/>
+      <c r="X129" s="54"/>
+      <c r="Y129" s="54"/>
+      <c r="Z129" s="54"/>
+      <c r="AA129" s="54"/>
+      <c r="AB129" s="54"/>
+      <c r="AC129" s="54"/>
+      <c r="AD129" s="54"/>
+      <c r="AE129" s="54"/>
+      <c r="AF129" s="54"/>
+      <c r="AG129" s="54"/>
+      <c r="AH129" s="54"/>
+      <c r="AI129" s="54"/>
+      <c r="AJ129" s="54"/>
+      <c r="AK129" s="55"/>
     </row>
     <row r="130" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
@@ -15891,45 +15924,45 @@
       <c r="AK140" s="1"/>
     </row>
     <row r="141" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="45" t="s">
+      <c r="A141" s="53" t="s">
         <v>530</v>
       </c>
-      <c r="B141" s="46"/>
-      <c r="C141" s="46"/>
-      <c r="D141" s="46"/>
-      <c r="E141" s="46"/>
-      <c r="F141" s="46"/>
-      <c r="G141" s="46"/>
-      <c r="H141" s="46"/>
-      <c r="I141" s="46"/>
-      <c r="J141" s="46"/>
-      <c r="K141" s="46"/>
-      <c r="L141" s="46"/>
-      <c r="M141" s="46"/>
-      <c r="N141" s="46"/>
-      <c r="O141" s="46"/>
-      <c r="P141" s="46"/>
-      <c r="Q141" s="46"/>
-      <c r="R141" s="46"/>
-      <c r="S141" s="46"/>
-      <c r="T141" s="46"/>
-      <c r="U141" s="46"/>
-      <c r="V141" s="46"/>
-      <c r="W141" s="46"/>
-      <c r="X141" s="46"/>
-      <c r="Y141" s="46"/>
-      <c r="Z141" s="46"/>
-      <c r="AA141" s="46"/>
-      <c r="AB141" s="46"/>
-      <c r="AC141" s="46"/>
-      <c r="AD141" s="46"/>
-      <c r="AE141" s="46"/>
-      <c r="AF141" s="46"/>
-      <c r="AG141" s="46"/>
-      <c r="AH141" s="46"/>
-      <c r="AI141" s="46"/>
-      <c r="AJ141" s="46"/>
-      <c r="AK141" s="47"/>
+      <c r="B141" s="54"/>
+      <c r="C141" s="54"/>
+      <c r="D141" s="54"/>
+      <c r="E141" s="54"/>
+      <c r="F141" s="54"/>
+      <c r="G141" s="54"/>
+      <c r="H141" s="54"/>
+      <c r="I141" s="54"/>
+      <c r="J141" s="54"/>
+      <c r="K141" s="54"/>
+      <c r="L141" s="54"/>
+      <c r="M141" s="54"/>
+      <c r="N141" s="54"/>
+      <c r="O141" s="54"/>
+      <c r="P141" s="54"/>
+      <c r="Q141" s="54"/>
+      <c r="R141" s="54"/>
+      <c r="S141" s="54"/>
+      <c r="T141" s="54"/>
+      <c r="U141" s="54"/>
+      <c r="V141" s="54"/>
+      <c r="W141" s="54"/>
+      <c r="X141" s="54"/>
+      <c r="Y141" s="54"/>
+      <c r="Z141" s="54"/>
+      <c r="AA141" s="54"/>
+      <c r="AB141" s="54"/>
+      <c r="AC141" s="54"/>
+      <c r="AD141" s="54"/>
+      <c r="AE141" s="54"/>
+      <c r="AF141" s="54"/>
+      <c r="AG141" s="54"/>
+      <c r="AH141" s="54"/>
+      <c r="AI141" s="54"/>
+      <c r="AJ141" s="54"/>
+      <c r="AK141" s="55"/>
     </row>
     <row r="142" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
@@ -16485,7 +16518,7 @@
       <c r="J151" s="2"/>
       <c r="K151" s="2"/>
       <c r="L151" s="2"/>
-      <c r="M151" s="52" t="s">
+      <c r="M151" s="46" t="s">
         <v>709</v>
       </c>
       <c r="N151" s="2"/>
@@ -16505,7 +16538,7 @@
       <c r="Z151" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AA151" s="52" t="s">
+      <c r="AA151" s="46" t="s">
         <v>709</v>
       </c>
       <c r="AB151" s="2"/>
@@ -16756,7 +16789,7 @@
       </c>
       <c r="K156" s="2"/>
       <c r="L156" s="2"/>
-      <c r="M156" s="52" t="s">
+      <c r="M156" s="46" t="s">
         <v>707</v>
       </c>
       <c r="N156" s="2"/>
@@ -16773,7 +16806,7 @@
       <c r="Y156" s="2">
         <v>1</v>
       </c>
-      <c r="Z156" s="52" t="s">
+      <c r="Z156" s="46" t="s">
         <v>707</v>
       </c>
       <c r="AA156" s="2"/>
@@ -16813,7 +16846,7 @@
       </c>
       <c r="K157" s="2"/>
       <c r="L157" s="2"/>
-      <c r="M157" s="52" t="s">
+      <c r="M157" s="46" t="s">
         <v>133</v>
       </c>
       <c r="N157" s="2"/>
@@ -16846,45 +16879,45 @@
       <c r="AK157" s="2"/>
     </row>
     <row r="158" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="48" t="s">
+      <c r="A158" s="56" t="s">
         <v>529</v>
       </c>
-      <c r="B158" s="49"/>
-      <c r="C158" s="49"/>
-      <c r="D158" s="49"/>
-      <c r="E158" s="49"/>
-      <c r="F158" s="49"/>
-      <c r="G158" s="49"/>
-      <c r="H158" s="49"/>
-      <c r="I158" s="49"/>
-      <c r="J158" s="49"/>
-      <c r="K158" s="49"/>
-      <c r="L158" s="49"/>
-      <c r="M158" s="49"/>
-      <c r="N158" s="49"/>
-      <c r="O158" s="49"/>
-      <c r="P158" s="49"/>
-      <c r="Q158" s="49"/>
-      <c r="R158" s="49"/>
-      <c r="S158" s="49"/>
-      <c r="T158" s="49"/>
-      <c r="U158" s="49"/>
-      <c r="V158" s="49"/>
-      <c r="W158" s="49"/>
-      <c r="X158" s="49"/>
-      <c r="Y158" s="49"/>
-      <c r="Z158" s="49"/>
-      <c r="AA158" s="49"/>
-      <c r="AB158" s="49"/>
-      <c r="AC158" s="49"/>
-      <c r="AD158" s="49"/>
-      <c r="AE158" s="49"/>
-      <c r="AF158" s="49"/>
-      <c r="AG158" s="49"/>
-      <c r="AH158" s="49"/>
-      <c r="AI158" s="49"/>
-      <c r="AJ158" s="49"/>
-      <c r="AK158" s="50"/>
+      <c r="B158" s="57"/>
+      <c r="C158" s="57"/>
+      <c r="D158" s="57"/>
+      <c r="E158" s="57"/>
+      <c r="F158" s="57"/>
+      <c r="G158" s="57"/>
+      <c r="H158" s="57"/>
+      <c r="I158" s="57"/>
+      <c r="J158" s="57"/>
+      <c r="K158" s="57"/>
+      <c r="L158" s="57"/>
+      <c r="M158" s="57"/>
+      <c r="N158" s="57"/>
+      <c r="O158" s="57"/>
+      <c r="P158" s="57"/>
+      <c r="Q158" s="57"/>
+      <c r="R158" s="57"/>
+      <c r="S158" s="57"/>
+      <c r="T158" s="57"/>
+      <c r="U158" s="57"/>
+      <c r="V158" s="57"/>
+      <c r="W158" s="57"/>
+      <c r="X158" s="57"/>
+      <c r="Y158" s="57"/>
+      <c r="Z158" s="57"/>
+      <c r="AA158" s="57"/>
+      <c r="AB158" s="57"/>
+      <c r="AC158" s="57"/>
+      <c r="AD158" s="57"/>
+      <c r="AE158" s="57"/>
+      <c r="AF158" s="57"/>
+      <c r="AG158" s="57"/>
+      <c r="AH158" s="57"/>
+      <c r="AI158" s="57"/>
+      <c r="AJ158" s="57"/>
+      <c r="AK158" s="58"/>
     </row>
     <row r="159" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
@@ -17121,45 +17154,45 @@
       <c r="AK162" s="1"/>
     </row>
     <row r="163" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="45" t="s">
+      <c r="A163" s="53" t="s">
         <v>528</v>
       </c>
-      <c r="B163" s="46"/>
-      <c r="C163" s="46"/>
-      <c r="D163" s="46"/>
-      <c r="E163" s="46"/>
-      <c r="F163" s="46"/>
-      <c r="G163" s="46"/>
-      <c r="H163" s="46"/>
-      <c r="I163" s="46"/>
-      <c r="J163" s="46"/>
-      <c r="K163" s="46"/>
-      <c r="L163" s="46"/>
-      <c r="M163" s="46"/>
-      <c r="N163" s="46"/>
-      <c r="O163" s="46"/>
-      <c r="P163" s="46"/>
-      <c r="Q163" s="46"/>
-      <c r="R163" s="46"/>
-      <c r="S163" s="46"/>
-      <c r="T163" s="46"/>
-      <c r="U163" s="46"/>
-      <c r="V163" s="46"/>
-      <c r="W163" s="46"/>
-      <c r="X163" s="46"/>
-      <c r="Y163" s="46"/>
-      <c r="Z163" s="46"/>
-      <c r="AA163" s="46"/>
-      <c r="AB163" s="46"/>
-      <c r="AC163" s="46"/>
-      <c r="AD163" s="46"/>
-      <c r="AE163" s="46"/>
-      <c r="AF163" s="46"/>
-      <c r="AG163" s="46"/>
-      <c r="AH163" s="46"/>
-      <c r="AI163" s="46"/>
-      <c r="AJ163" s="46"/>
-      <c r="AK163" s="47"/>
+      <c r="B163" s="54"/>
+      <c r="C163" s="54"/>
+      <c r="D163" s="54"/>
+      <c r="E163" s="54"/>
+      <c r="F163" s="54"/>
+      <c r="G163" s="54"/>
+      <c r="H163" s="54"/>
+      <c r="I163" s="54"/>
+      <c r="J163" s="54"/>
+      <c r="K163" s="54"/>
+      <c r="L163" s="54"/>
+      <c r="M163" s="54"/>
+      <c r="N163" s="54"/>
+      <c r="O163" s="54"/>
+      <c r="P163" s="54"/>
+      <c r="Q163" s="54"/>
+      <c r="R163" s="54"/>
+      <c r="S163" s="54"/>
+      <c r="T163" s="54"/>
+      <c r="U163" s="54"/>
+      <c r="V163" s="54"/>
+      <c r="W163" s="54"/>
+      <c r="X163" s="54"/>
+      <c r="Y163" s="54"/>
+      <c r="Z163" s="54"/>
+      <c r="AA163" s="54"/>
+      <c r="AB163" s="54"/>
+      <c r="AC163" s="54"/>
+      <c r="AD163" s="54"/>
+      <c r="AE163" s="54"/>
+      <c r="AF163" s="54"/>
+      <c r="AG163" s="54"/>
+      <c r="AH163" s="54"/>
+      <c r="AI163" s="54"/>
+      <c r="AJ163" s="54"/>
+      <c r="AK163" s="55"/>
     </row>
     <row r="164" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
@@ -17451,45 +17484,45 @@
       <c r="AK168" s="1"/>
     </row>
     <row r="169" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="45" t="s">
+      <c r="A169" s="53" t="s">
         <v>527</v>
       </c>
-      <c r="B169" s="46"/>
-      <c r="C169" s="46"/>
-      <c r="D169" s="46"/>
-      <c r="E169" s="46"/>
-      <c r="F169" s="46"/>
-      <c r="G169" s="46"/>
-      <c r="H169" s="46"/>
-      <c r="I169" s="46"/>
-      <c r="J169" s="46"/>
-      <c r="K169" s="46"/>
-      <c r="L169" s="46"/>
-      <c r="M169" s="46"/>
-      <c r="N169" s="46"/>
-      <c r="O169" s="46"/>
-      <c r="P169" s="46"/>
-      <c r="Q169" s="46"/>
-      <c r="R169" s="46"/>
-      <c r="S169" s="46"/>
-      <c r="T169" s="46"/>
-      <c r="U169" s="46"/>
-      <c r="V169" s="46"/>
-      <c r="W169" s="46"/>
-      <c r="X169" s="46"/>
-      <c r="Y169" s="46"/>
-      <c r="Z169" s="46"/>
-      <c r="AA169" s="46"/>
-      <c r="AB169" s="46"/>
-      <c r="AC169" s="46"/>
-      <c r="AD169" s="46"/>
-      <c r="AE169" s="46"/>
-      <c r="AF169" s="46"/>
-      <c r="AG169" s="46"/>
-      <c r="AH169" s="46"/>
-      <c r="AI169" s="46"/>
-      <c r="AJ169" s="46"/>
-      <c r="AK169" s="47"/>
+      <c r="B169" s="54"/>
+      <c r="C169" s="54"/>
+      <c r="D169" s="54"/>
+      <c r="E169" s="54"/>
+      <c r="F169" s="54"/>
+      <c r="G169" s="54"/>
+      <c r="H169" s="54"/>
+      <c r="I169" s="54"/>
+      <c r="J169" s="54"/>
+      <c r="K169" s="54"/>
+      <c r="L169" s="54"/>
+      <c r="M169" s="54"/>
+      <c r="N169" s="54"/>
+      <c r="O169" s="54"/>
+      <c r="P169" s="54"/>
+      <c r="Q169" s="54"/>
+      <c r="R169" s="54"/>
+      <c r="S169" s="54"/>
+      <c r="T169" s="54"/>
+      <c r="U169" s="54"/>
+      <c r="V169" s="54"/>
+      <c r="W169" s="54"/>
+      <c r="X169" s="54"/>
+      <c r="Y169" s="54"/>
+      <c r="Z169" s="54"/>
+      <c r="AA169" s="54"/>
+      <c r="AB169" s="54"/>
+      <c r="AC169" s="54"/>
+      <c r="AD169" s="54"/>
+      <c r="AE169" s="54"/>
+      <c r="AF169" s="54"/>
+      <c r="AG169" s="54"/>
+      <c r="AH169" s="54"/>
+      <c r="AI169" s="54"/>
+      <c r="AJ169" s="54"/>
+      <c r="AK169" s="55"/>
     </row>
     <row r="170" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
@@ -17952,45 +17985,45 @@
       <c r="AK177" s="1"/>
     </row>
     <row r="178" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A178" s="45" t="s">
+      <c r="A178" s="53" t="s">
         <v>526</v>
       </c>
-      <c r="B178" s="46"/>
-      <c r="C178" s="46"/>
-      <c r="D178" s="46"/>
-      <c r="E178" s="46"/>
-      <c r="F178" s="46"/>
-      <c r="G178" s="46"/>
-      <c r="H178" s="46"/>
-      <c r="I178" s="46"/>
-      <c r="J178" s="46"/>
-      <c r="K178" s="46"/>
-      <c r="L178" s="46"/>
-      <c r="M178" s="46"/>
-      <c r="N178" s="46"/>
-      <c r="O178" s="46"/>
-      <c r="P178" s="46"/>
-      <c r="Q178" s="46"/>
-      <c r="R178" s="46"/>
-      <c r="S178" s="46"/>
-      <c r="T178" s="46"/>
-      <c r="U178" s="46"/>
-      <c r="V178" s="46"/>
-      <c r="W178" s="46"/>
-      <c r="X178" s="46"/>
-      <c r="Y178" s="46"/>
-      <c r="Z178" s="46"/>
-      <c r="AA178" s="46"/>
-      <c r="AB178" s="46"/>
-      <c r="AC178" s="46"/>
-      <c r="AD178" s="46"/>
-      <c r="AE178" s="46"/>
-      <c r="AF178" s="46"/>
-      <c r="AG178" s="46"/>
-      <c r="AH178" s="46"/>
-      <c r="AI178" s="46"/>
-      <c r="AJ178" s="46"/>
-      <c r="AK178" s="47"/>
+      <c r="B178" s="54"/>
+      <c r="C178" s="54"/>
+      <c r="D178" s="54"/>
+      <c r="E178" s="54"/>
+      <c r="F178" s="54"/>
+      <c r="G178" s="54"/>
+      <c r="H178" s="54"/>
+      <c r="I178" s="54"/>
+      <c r="J178" s="54"/>
+      <c r="K178" s="54"/>
+      <c r="L178" s="54"/>
+      <c r="M178" s="54"/>
+      <c r="N178" s="54"/>
+      <c r="O178" s="54"/>
+      <c r="P178" s="54"/>
+      <c r="Q178" s="54"/>
+      <c r="R178" s="54"/>
+      <c r="S178" s="54"/>
+      <c r="T178" s="54"/>
+      <c r="U178" s="54"/>
+      <c r="V178" s="54"/>
+      <c r="W178" s="54"/>
+      <c r="X178" s="54"/>
+      <c r="Y178" s="54"/>
+      <c r="Z178" s="54"/>
+      <c r="AA178" s="54"/>
+      <c r="AB178" s="54"/>
+      <c r="AC178" s="54"/>
+      <c r="AD178" s="54"/>
+      <c r="AE178" s="54"/>
+      <c r="AF178" s="54"/>
+      <c r="AG178" s="54"/>
+      <c r="AH178" s="54"/>
+      <c r="AI178" s="54"/>
+      <c r="AJ178" s="54"/>
+      <c r="AK178" s="55"/>
     </row>
     <row r="179" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A179" s="26" t="s">
@@ -18398,45 +18431,45 @@
       <c r="AK185" s="1"/>
     </row>
     <row r="186" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A186" s="45" t="s">
+      <c r="A186" s="53" t="s">
         <v>534</v>
       </c>
-      <c r="B186" s="46"/>
-      <c r="C186" s="46"/>
-      <c r="D186" s="46"/>
-      <c r="E186" s="46"/>
-      <c r="F186" s="46"/>
-      <c r="G186" s="46"/>
-      <c r="H186" s="46"/>
-      <c r="I186" s="46"/>
-      <c r="J186" s="46"/>
-      <c r="K186" s="46"/>
-      <c r="L186" s="46"/>
-      <c r="M186" s="46"/>
-      <c r="N186" s="46"/>
-      <c r="O186" s="46"/>
-      <c r="P186" s="46"/>
-      <c r="Q186" s="46"/>
-      <c r="R186" s="46"/>
-      <c r="S186" s="46"/>
-      <c r="T186" s="46"/>
-      <c r="U186" s="46"/>
-      <c r="V186" s="46"/>
-      <c r="W186" s="46"/>
-      <c r="X186" s="46"/>
-      <c r="Y186" s="46"/>
-      <c r="Z186" s="46"/>
-      <c r="AA186" s="46"/>
-      <c r="AB186" s="46"/>
-      <c r="AC186" s="46"/>
-      <c r="AD186" s="46"/>
-      <c r="AE186" s="46"/>
-      <c r="AF186" s="46"/>
-      <c r="AG186" s="46"/>
-      <c r="AH186" s="46"/>
-      <c r="AI186" s="46"/>
-      <c r="AJ186" s="46"/>
-      <c r="AK186" s="47"/>
+      <c r="B186" s="54"/>
+      <c r="C186" s="54"/>
+      <c r="D186" s="54"/>
+      <c r="E186" s="54"/>
+      <c r="F186" s="54"/>
+      <c r="G186" s="54"/>
+      <c r="H186" s="54"/>
+      <c r="I186" s="54"/>
+      <c r="J186" s="54"/>
+      <c r="K186" s="54"/>
+      <c r="L186" s="54"/>
+      <c r="M186" s="54"/>
+      <c r="N186" s="54"/>
+      <c r="O186" s="54"/>
+      <c r="P186" s="54"/>
+      <c r="Q186" s="54"/>
+      <c r="R186" s="54"/>
+      <c r="S186" s="54"/>
+      <c r="T186" s="54"/>
+      <c r="U186" s="54"/>
+      <c r="V186" s="54"/>
+      <c r="W186" s="54"/>
+      <c r="X186" s="54"/>
+      <c r="Y186" s="54"/>
+      <c r="Z186" s="54"/>
+      <c r="AA186" s="54"/>
+      <c r="AB186" s="54"/>
+      <c r="AC186" s="54"/>
+      <c r="AD186" s="54"/>
+      <c r="AE186" s="54"/>
+      <c r="AF186" s="54"/>
+      <c r="AG186" s="54"/>
+      <c r="AH186" s="54"/>
+      <c r="AI186" s="54"/>
+      <c r="AJ186" s="54"/>
+      <c r="AK186" s="55"/>
     </row>
     <row r="187" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
@@ -19213,45 +19246,45 @@
       <c r="AK200" s="2"/>
     </row>
     <row r="201" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="45" t="s">
+      <c r="A201" s="53" t="s">
         <v>535</v>
       </c>
-      <c r="B201" s="46"/>
-      <c r="C201" s="46"/>
-      <c r="D201" s="46"/>
-      <c r="E201" s="46"/>
-      <c r="F201" s="46"/>
-      <c r="G201" s="46"/>
-      <c r="H201" s="46"/>
-      <c r="I201" s="46"/>
-      <c r="J201" s="46"/>
-      <c r="K201" s="46"/>
-      <c r="L201" s="46"/>
-      <c r="M201" s="46"/>
-      <c r="N201" s="46"/>
-      <c r="O201" s="46"/>
-      <c r="P201" s="46"/>
-      <c r="Q201" s="46"/>
-      <c r="R201" s="46"/>
-      <c r="S201" s="46"/>
-      <c r="T201" s="46"/>
-      <c r="U201" s="46"/>
-      <c r="V201" s="46"/>
-      <c r="W201" s="46"/>
-      <c r="X201" s="46"/>
-      <c r="Y201" s="46"/>
-      <c r="Z201" s="46"/>
-      <c r="AA201" s="46"/>
-      <c r="AB201" s="46"/>
-      <c r="AC201" s="46"/>
-      <c r="AD201" s="46"/>
-      <c r="AE201" s="46"/>
-      <c r="AF201" s="46"/>
-      <c r="AG201" s="46"/>
-      <c r="AH201" s="46"/>
-      <c r="AI201" s="46"/>
-      <c r="AJ201" s="46"/>
-      <c r="AK201" s="47"/>
+      <c r="B201" s="54"/>
+      <c r="C201" s="54"/>
+      <c r="D201" s="54"/>
+      <c r="E201" s="54"/>
+      <c r="F201" s="54"/>
+      <c r="G201" s="54"/>
+      <c r="H201" s="54"/>
+      <c r="I201" s="54"/>
+      <c r="J201" s="54"/>
+      <c r="K201" s="54"/>
+      <c r="L201" s="54"/>
+      <c r="M201" s="54"/>
+      <c r="N201" s="54"/>
+      <c r="O201" s="54"/>
+      <c r="P201" s="54"/>
+      <c r="Q201" s="54"/>
+      <c r="R201" s="54"/>
+      <c r="S201" s="54"/>
+      <c r="T201" s="54"/>
+      <c r="U201" s="54"/>
+      <c r="V201" s="54"/>
+      <c r="W201" s="54"/>
+      <c r="X201" s="54"/>
+      <c r="Y201" s="54"/>
+      <c r="Z201" s="54"/>
+      <c r="AA201" s="54"/>
+      <c r="AB201" s="54"/>
+      <c r="AC201" s="54"/>
+      <c r="AD201" s="54"/>
+      <c r="AE201" s="54"/>
+      <c r="AF201" s="54"/>
+      <c r="AG201" s="54"/>
+      <c r="AH201" s="54"/>
+      <c r="AI201" s="54"/>
+      <c r="AJ201" s="54"/>
+      <c r="AK201" s="55"/>
     </row>
     <row r="202" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
@@ -19586,45 +19619,45 @@
       <c r="AK207" s="1"/>
     </row>
     <row r="208" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="45" t="s">
+      <c r="A208" s="53" t="s">
         <v>549</v>
       </c>
-      <c r="B208" s="46"/>
-      <c r="C208" s="46"/>
-      <c r="D208" s="46"/>
-      <c r="E208" s="46"/>
-      <c r="F208" s="46"/>
-      <c r="G208" s="46"/>
-      <c r="H208" s="46"/>
-      <c r="I208" s="46"/>
-      <c r="J208" s="46"/>
-      <c r="K208" s="46"/>
-      <c r="L208" s="46"/>
-      <c r="M208" s="46"/>
-      <c r="N208" s="46"/>
-      <c r="O208" s="46"/>
-      <c r="P208" s="46"/>
-      <c r="Q208" s="46"/>
-      <c r="R208" s="46"/>
-      <c r="S208" s="46"/>
-      <c r="T208" s="46"/>
-      <c r="U208" s="46"/>
-      <c r="V208" s="46"/>
-      <c r="W208" s="46"/>
-      <c r="X208" s="46"/>
-      <c r="Y208" s="46"/>
-      <c r="Z208" s="46"/>
-      <c r="AA208" s="46"/>
-      <c r="AB208" s="46"/>
-      <c r="AC208" s="46"/>
-      <c r="AD208" s="46"/>
-      <c r="AE208" s="46"/>
-      <c r="AF208" s="46"/>
-      <c r="AG208" s="46"/>
-      <c r="AH208" s="46"/>
-      <c r="AI208" s="46"/>
-      <c r="AJ208" s="46"/>
-      <c r="AK208" s="47"/>
+      <c r="B208" s="54"/>
+      <c r="C208" s="54"/>
+      <c r="D208" s="54"/>
+      <c r="E208" s="54"/>
+      <c r="F208" s="54"/>
+      <c r="G208" s="54"/>
+      <c r="H208" s="54"/>
+      <c r="I208" s="54"/>
+      <c r="J208" s="54"/>
+      <c r="K208" s="54"/>
+      <c r="L208" s="54"/>
+      <c r="M208" s="54"/>
+      <c r="N208" s="54"/>
+      <c r="O208" s="54"/>
+      <c r="P208" s="54"/>
+      <c r="Q208" s="54"/>
+      <c r="R208" s="54"/>
+      <c r="S208" s="54"/>
+      <c r="T208" s="54"/>
+      <c r="U208" s="54"/>
+      <c r="V208" s="54"/>
+      <c r="W208" s="54"/>
+      <c r="X208" s="54"/>
+      <c r="Y208" s="54"/>
+      <c r="Z208" s="54"/>
+      <c r="AA208" s="54"/>
+      <c r="AB208" s="54"/>
+      <c r="AC208" s="54"/>
+      <c r="AD208" s="54"/>
+      <c r="AE208" s="54"/>
+      <c r="AF208" s="54"/>
+      <c r="AG208" s="54"/>
+      <c r="AH208" s="54"/>
+      <c r="AI208" s="54"/>
+      <c r="AJ208" s="54"/>
+      <c r="AK208" s="55"/>
     </row>
     <row r="209" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
@@ -19963,45 +19996,45 @@
       <c r="AK214" s="1"/>
     </row>
     <row r="215" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="45" t="s">
+      <c r="A215" s="53" t="s">
         <v>740</v>
       </c>
-      <c r="B215" s="46"/>
-      <c r="C215" s="46"/>
-      <c r="D215" s="46"/>
-      <c r="E215" s="46"/>
-      <c r="F215" s="46"/>
-      <c r="G215" s="46"/>
-      <c r="H215" s="46"/>
-      <c r="I215" s="46"/>
-      <c r="J215" s="46"/>
-      <c r="K215" s="46"/>
-      <c r="L215" s="46"/>
-      <c r="M215" s="46"/>
-      <c r="N215" s="46"/>
-      <c r="O215" s="46"/>
-      <c r="P215" s="46"/>
-      <c r="Q215" s="46"/>
-      <c r="R215" s="46"/>
-      <c r="S215" s="46"/>
-      <c r="T215" s="46"/>
-      <c r="U215" s="46"/>
-      <c r="V215" s="46"/>
-      <c r="W215" s="46"/>
-      <c r="X215" s="46"/>
-      <c r="Y215" s="46"/>
-      <c r="Z215" s="46"/>
-      <c r="AA215" s="46"/>
-      <c r="AB215" s="46"/>
-      <c r="AC215" s="46"/>
-      <c r="AD215" s="46"/>
-      <c r="AE215" s="46"/>
-      <c r="AF215" s="46"/>
-      <c r="AG215" s="46"/>
-      <c r="AH215" s="46"/>
-      <c r="AI215" s="46"/>
-      <c r="AJ215" s="46"/>
-      <c r="AK215" s="47"/>
+      <c r="B215" s="54"/>
+      <c r="C215" s="54"/>
+      <c r="D215" s="54"/>
+      <c r="E215" s="54"/>
+      <c r="F215" s="54"/>
+      <c r="G215" s="54"/>
+      <c r="H215" s="54"/>
+      <c r="I215" s="54"/>
+      <c r="J215" s="54"/>
+      <c r="K215" s="54"/>
+      <c r="L215" s="54"/>
+      <c r="M215" s="54"/>
+      <c r="N215" s="54"/>
+      <c r="O215" s="54"/>
+      <c r="P215" s="54"/>
+      <c r="Q215" s="54"/>
+      <c r="R215" s="54"/>
+      <c r="S215" s="54"/>
+      <c r="T215" s="54"/>
+      <c r="U215" s="54"/>
+      <c r="V215" s="54"/>
+      <c r="W215" s="54"/>
+      <c r="X215" s="54"/>
+      <c r="Y215" s="54"/>
+      <c r="Z215" s="54"/>
+      <c r="AA215" s="54"/>
+      <c r="AB215" s="54"/>
+      <c r="AC215" s="54"/>
+      <c r="AD215" s="54"/>
+      <c r="AE215" s="54"/>
+      <c r="AF215" s="54"/>
+      <c r="AG215" s="54"/>
+      <c r="AH215" s="54"/>
+      <c r="AI215" s="54"/>
+      <c r="AJ215" s="54"/>
+      <c r="AK215" s="55"/>
     </row>
     <row r="216" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
@@ -20611,45 +20644,45 @@
       <c r="AK226" s="1"/>
     </row>
     <row r="227" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A227" s="45" t="s">
+      <c r="A227" s="53" t="s">
         <v>741</v>
       </c>
-      <c r="B227" s="46"/>
-      <c r="C227" s="46"/>
-      <c r="D227" s="46"/>
-      <c r="E227" s="46"/>
-      <c r="F227" s="46"/>
-      <c r="G227" s="46"/>
-      <c r="H227" s="46"/>
-      <c r="I227" s="46"/>
-      <c r="J227" s="46"/>
-      <c r="K227" s="46"/>
-      <c r="L227" s="46"/>
-      <c r="M227" s="46"/>
-      <c r="N227" s="46"/>
-      <c r="O227" s="46"/>
-      <c r="P227" s="46"/>
-      <c r="Q227" s="46"/>
-      <c r="R227" s="46"/>
-      <c r="S227" s="46"/>
-      <c r="T227" s="46"/>
-      <c r="U227" s="46"/>
-      <c r="V227" s="46"/>
-      <c r="W227" s="46"/>
-      <c r="X227" s="46"/>
-      <c r="Y227" s="46"/>
-      <c r="Z227" s="46"/>
-      <c r="AA227" s="46"/>
-      <c r="AB227" s="46"/>
-      <c r="AC227" s="46"/>
-      <c r="AD227" s="46"/>
-      <c r="AE227" s="46"/>
-      <c r="AF227" s="46"/>
-      <c r="AG227" s="46"/>
-      <c r="AH227" s="46"/>
-      <c r="AI227" s="46"/>
-      <c r="AJ227" s="46"/>
-      <c r="AK227" s="47"/>
+      <c r="B227" s="54"/>
+      <c r="C227" s="54"/>
+      <c r="D227" s="54"/>
+      <c r="E227" s="54"/>
+      <c r="F227" s="54"/>
+      <c r="G227" s="54"/>
+      <c r="H227" s="54"/>
+      <c r="I227" s="54"/>
+      <c r="J227" s="54"/>
+      <c r="K227" s="54"/>
+      <c r="L227" s="54"/>
+      <c r="M227" s="54"/>
+      <c r="N227" s="54"/>
+      <c r="O227" s="54"/>
+      <c r="P227" s="54"/>
+      <c r="Q227" s="54"/>
+      <c r="R227" s="54"/>
+      <c r="S227" s="54"/>
+      <c r="T227" s="54"/>
+      <c r="U227" s="54"/>
+      <c r="V227" s="54"/>
+      <c r="W227" s="54"/>
+      <c r="X227" s="54"/>
+      <c r="Y227" s="54"/>
+      <c r="Z227" s="54"/>
+      <c r="AA227" s="54"/>
+      <c r="AB227" s="54"/>
+      <c r="AC227" s="54"/>
+      <c r="AD227" s="54"/>
+      <c r="AE227" s="54"/>
+      <c r="AF227" s="54"/>
+      <c r="AG227" s="54"/>
+      <c r="AH227" s="54"/>
+      <c r="AI227" s="54"/>
+      <c r="AJ227" s="54"/>
+      <c r="AK227" s="55"/>
     </row>
     <row r="228" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
@@ -20904,7 +20937,7 @@
       <c r="L232" s="1">
         <v>1</v>
       </c>
-      <c r="M232" s="53" t="s">
+      <c r="M232" s="47" t="s">
         <v>657</v>
       </c>
       <c r="N232" s="2"/>
@@ -21161,45 +21194,45 @@
       <c r="AK236" s="1"/>
     </row>
     <row r="237" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A237" s="45" t="s">
+      <c r="A237" s="53" t="s">
         <v>638</v>
       </c>
-      <c r="B237" s="46"/>
-      <c r="C237" s="46"/>
-      <c r="D237" s="46"/>
-      <c r="E237" s="46"/>
-      <c r="F237" s="46"/>
-      <c r="G237" s="46"/>
-      <c r="H237" s="46"/>
-      <c r="I237" s="46"/>
-      <c r="J237" s="46"/>
-      <c r="K237" s="46"/>
-      <c r="L237" s="46"/>
-      <c r="M237" s="46"/>
-      <c r="N237" s="46"/>
-      <c r="O237" s="46"/>
-      <c r="P237" s="46"/>
-      <c r="Q237" s="46"/>
-      <c r="R237" s="46"/>
-      <c r="S237" s="46"/>
-      <c r="T237" s="46"/>
-      <c r="U237" s="46"/>
-      <c r="V237" s="46"/>
-      <c r="W237" s="46"/>
-      <c r="X237" s="46"/>
-      <c r="Y237" s="46"/>
-      <c r="Z237" s="46"/>
-      <c r="AA237" s="46"/>
-      <c r="AB237" s="46"/>
-      <c r="AC237" s="46"/>
-      <c r="AD237" s="46"/>
-      <c r="AE237" s="46"/>
-      <c r="AF237" s="46"/>
-      <c r="AG237" s="46"/>
-      <c r="AH237" s="46"/>
-      <c r="AI237" s="46"/>
-      <c r="AJ237" s="46"/>
-      <c r="AK237" s="47"/>
+      <c r="B237" s="54"/>
+      <c r="C237" s="54"/>
+      <c r="D237" s="54"/>
+      <c r="E237" s="54"/>
+      <c r="F237" s="54"/>
+      <c r="G237" s="54"/>
+      <c r="H237" s="54"/>
+      <c r="I237" s="54"/>
+      <c r="J237" s="54"/>
+      <c r="K237" s="54"/>
+      <c r="L237" s="54"/>
+      <c r="M237" s="54"/>
+      <c r="N237" s="54"/>
+      <c r="O237" s="54"/>
+      <c r="P237" s="54"/>
+      <c r="Q237" s="54"/>
+      <c r="R237" s="54"/>
+      <c r="S237" s="54"/>
+      <c r="T237" s="54"/>
+      <c r="U237" s="54"/>
+      <c r="V237" s="54"/>
+      <c r="W237" s="54"/>
+      <c r="X237" s="54"/>
+      <c r="Y237" s="54"/>
+      <c r="Z237" s="54"/>
+      <c r="AA237" s="54"/>
+      <c r="AB237" s="54"/>
+      <c r="AC237" s="54"/>
+      <c r="AD237" s="54"/>
+      <c r="AE237" s="54"/>
+      <c r="AF237" s="54"/>
+      <c r="AG237" s="54"/>
+      <c r="AH237" s="54"/>
+      <c r="AI237" s="54"/>
+      <c r="AJ237" s="54"/>
+      <c r="AK237" s="55"/>
     </row>
     <row r="238" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
@@ -21493,45 +21526,45 @@
       <c r="AK242" s="1"/>
     </row>
     <row r="243" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A243" s="45" t="s">
+      <c r="A243" s="53" t="s">
         <v>697</v>
       </c>
-      <c r="B243" s="46"/>
-      <c r="C243" s="46"/>
-      <c r="D243" s="46"/>
-      <c r="E243" s="46"/>
-      <c r="F243" s="46"/>
-      <c r="G243" s="46"/>
-      <c r="H243" s="46"/>
-      <c r="I243" s="46"/>
-      <c r="J243" s="46"/>
-      <c r="K243" s="46"/>
-      <c r="L243" s="46"/>
-      <c r="M243" s="46"/>
-      <c r="N243" s="46"/>
-      <c r="O243" s="46"/>
-      <c r="P243" s="46"/>
-      <c r="Q243" s="46"/>
-      <c r="R243" s="46"/>
-      <c r="S243" s="46"/>
-      <c r="T243" s="46"/>
-      <c r="U243" s="46"/>
-      <c r="V243" s="46"/>
-      <c r="W243" s="46"/>
-      <c r="X243" s="46"/>
-      <c r="Y243" s="46"/>
-      <c r="Z243" s="46"/>
-      <c r="AA243" s="46"/>
-      <c r="AB243" s="46"/>
-      <c r="AC243" s="46"/>
-      <c r="AD243" s="46"/>
-      <c r="AE243" s="46"/>
-      <c r="AF243" s="46"/>
-      <c r="AG243" s="46"/>
-      <c r="AH243" s="46"/>
-      <c r="AI243" s="46"/>
-      <c r="AJ243" s="46"/>
-      <c r="AK243" s="47"/>
+      <c r="B243" s="54"/>
+      <c r="C243" s="54"/>
+      <c r="D243" s="54"/>
+      <c r="E243" s="54"/>
+      <c r="F243" s="54"/>
+      <c r="G243" s="54"/>
+      <c r="H243" s="54"/>
+      <c r="I243" s="54"/>
+      <c r="J243" s="54"/>
+      <c r="K243" s="54"/>
+      <c r="L243" s="54"/>
+      <c r="M243" s="54"/>
+      <c r="N243" s="54"/>
+      <c r="O243" s="54"/>
+      <c r="P243" s="54"/>
+      <c r="Q243" s="54"/>
+      <c r="R243" s="54"/>
+      <c r="S243" s="54"/>
+      <c r="T243" s="54"/>
+      <c r="U243" s="54"/>
+      <c r="V243" s="54"/>
+      <c r="W243" s="54"/>
+      <c r="X243" s="54"/>
+      <c r="Y243" s="54"/>
+      <c r="Z243" s="54"/>
+      <c r="AA243" s="54"/>
+      <c r="AB243" s="54"/>
+      <c r="AC243" s="54"/>
+      <c r="AD243" s="54"/>
+      <c r="AE243" s="54"/>
+      <c r="AF243" s="54"/>
+      <c r="AG243" s="54"/>
+      <c r="AH243" s="54"/>
+      <c r="AI243" s="54"/>
+      <c r="AJ243" s="54"/>
+      <c r="AK243" s="55"/>
     </row>
     <row r="244" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A244" s="26" t="s">
@@ -21823,45 +21856,45 @@
       <c r="AK248" s="1"/>
     </row>
     <row r="249" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A249" s="45" t="s">
+      <c r="A249" s="53" t="s">
         <v>696</v>
       </c>
-      <c r="B249" s="46"/>
-      <c r="C249" s="46"/>
-      <c r="D249" s="46"/>
-      <c r="E249" s="46"/>
-      <c r="F249" s="46"/>
-      <c r="G249" s="46"/>
-      <c r="H249" s="46"/>
-      <c r="I249" s="46"/>
-      <c r="J249" s="46"/>
-      <c r="K249" s="46"/>
-      <c r="L249" s="46"/>
-      <c r="M249" s="46"/>
-      <c r="N249" s="46"/>
-      <c r="O249" s="46"/>
-      <c r="P249" s="46"/>
-      <c r="Q249" s="46"/>
-      <c r="R249" s="46"/>
-      <c r="S249" s="46"/>
-      <c r="T249" s="46"/>
-      <c r="U249" s="46"/>
-      <c r="V249" s="46"/>
-      <c r="W249" s="46"/>
-      <c r="X249" s="46"/>
-      <c r="Y249" s="46"/>
-      <c r="Z249" s="46"/>
-      <c r="AA249" s="46"/>
-      <c r="AB249" s="46"/>
-      <c r="AC249" s="46"/>
-      <c r="AD249" s="46"/>
-      <c r="AE249" s="46"/>
-      <c r="AF249" s="46"/>
-      <c r="AG249" s="46"/>
-      <c r="AH249" s="46"/>
-      <c r="AI249" s="46"/>
-      <c r="AJ249" s="46"/>
-      <c r="AK249" s="47"/>
+      <c r="B249" s="54"/>
+      <c r="C249" s="54"/>
+      <c r="D249" s="54"/>
+      <c r="E249" s="54"/>
+      <c r="F249" s="54"/>
+      <c r="G249" s="54"/>
+      <c r="H249" s="54"/>
+      <c r="I249" s="54"/>
+      <c r="J249" s="54"/>
+      <c r="K249" s="54"/>
+      <c r="L249" s="54"/>
+      <c r="M249" s="54"/>
+      <c r="N249" s="54"/>
+      <c r="O249" s="54"/>
+      <c r="P249" s="54"/>
+      <c r="Q249" s="54"/>
+      <c r="R249" s="54"/>
+      <c r="S249" s="54"/>
+      <c r="T249" s="54"/>
+      <c r="U249" s="54"/>
+      <c r="V249" s="54"/>
+      <c r="W249" s="54"/>
+      <c r="X249" s="54"/>
+      <c r="Y249" s="54"/>
+      <c r="Z249" s="54"/>
+      <c r="AA249" s="54"/>
+      <c r="AB249" s="54"/>
+      <c r="AC249" s="54"/>
+      <c r="AD249" s="54"/>
+      <c r="AE249" s="54"/>
+      <c r="AF249" s="54"/>
+      <c r="AG249" s="54"/>
+      <c r="AH249" s="54"/>
+      <c r="AI249" s="54"/>
+      <c r="AJ249" s="54"/>
+      <c r="AK249" s="55"/>
     </row>
     <row r="250" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A250" s="26" t="s">
@@ -22039,45 +22072,45 @@
       <c r="AK252" s="1"/>
     </row>
     <row r="253" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A253" s="45" t="s">
+      <c r="A253" s="53" t="s">
         <v>694</v>
       </c>
-      <c r="B253" s="46"/>
-      <c r="C253" s="46"/>
-      <c r="D253" s="46"/>
-      <c r="E253" s="46"/>
-      <c r="F253" s="46"/>
-      <c r="G253" s="46"/>
-      <c r="H253" s="46"/>
-      <c r="I253" s="46"/>
-      <c r="J253" s="46"/>
-      <c r="K253" s="46"/>
-      <c r="L253" s="46"/>
-      <c r="M253" s="46"/>
-      <c r="N253" s="46"/>
-      <c r="O253" s="46"/>
-      <c r="P253" s="46"/>
-      <c r="Q253" s="46"/>
-      <c r="R253" s="46"/>
-      <c r="S253" s="46"/>
-      <c r="T253" s="46"/>
-      <c r="U253" s="46"/>
-      <c r="V253" s="46"/>
-      <c r="W253" s="46"/>
-      <c r="X253" s="46"/>
-      <c r="Y253" s="46"/>
-      <c r="Z253" s="46"/>
-      <c r="AA253" s="46"/>
-      <c r="AB253" s="46"/>
-      <c r="AC253" s="46"/>
-      <c r="AD253" s="46"/>
-      <c r="AE253" s="46"/>
-      <c r="AF253" s="46"/>
-      <c r="AG253" s="46"/>
-      <c r="AH253" s="46"/>
-      <c r="AI253" s="46"/>
-      <c r="AJ253" s="46"/>
-      <c r="AK253" s="47"/>
+      <c r="B253" s="54"/>
+      <c r="C253" s="54"/>
+      <c r="D253" s="54"/>
+      <c r="E253" s="54"/>
+      <c r="F253" s="54"/>
+      <c r="G253" s="54"/>
+      <c r="H253" s="54"/>
+      <c r="I253" s="54"/>
+      <c r="J253" s="54"/>
+      <c r="K253" s="54"/>
+      <c r="L253" s="54"/>
+      <c r="M253" s="54"/>
+      <c r="N253" s="54"/>
+      <c r="O253" s="54"/>
+      <c r="P253" s="54"/>
+      <c r="Q253" s="54"/>
+      <c r="R253" s="54"/>
+      <c r="S253" s="54"/>
+      <c r="T253" s="54"/>
+      <c r="U253" s="54"/>
+      <c r="V253" s="54"/>
+      <c r="W253" s="54"/>
+      <c r="X253" s="54"/>
+      <c r="Y253" s="54"/>
+      <c r="Z253" s="54"/>
+      <c r="AA253" s="54"/>
+      <c r="AB253" s="54"/>
+      <c r="AC253" s="54"/>
+      <c r="AD253" s="54"/>
+      <c r="AE253" s="54"/>
+      <c r="AF253" s="54"/>
+      <c r="AG253" s="54"/>
+      <c r="AH253" s="54"/>
+      <c r="AI253" s="54"/>
+      <c r="AJ253" s="54"/>
+      <c r="AK253" s="55"/>
     </row>
     <row r="254" spans="1:37" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
@@ -22237,6 +22270,14 @@
   </sheetData>
   <autoFilter ref="A1:AJ256" xr:uid="{0580B1DF-60C2-4E2B-940A-667729080FCF}"/>
   <mergeCells count="17">
+    <mergeCell ref="A169:AK169"/>
+    <mergeCell ref="A2:AK2"/>
+    <mergeCell ref="A60:AK60"/>
+    <mergeCell ref="A253:AK253"/>
+    <mergeCell ref="A249:AK249"/>
+    <mergeCell ref="A243:AK243"/>
+    <mergeCell ref="A237:AK237"/>
+    <mergeCell ref="A227:AK227"/>
     <mergeCell ref="A215:AK215"/>
     <mergeCell ref="A163:AK163"/>
     <mergeCell ref="A158:AK158"/>
@@ -22244,16 +22285,8 @@
     <mergeCell ref="A129:AK129"/>
     <mergeCell ref="A208:AK208"/>
     <mergeCell ref="A201:AK201"/>
-    <mergeCell ref="A253:AK253"/>
-    <mergeCell ref="A249:AK249"/>
-    <mergeCell ref="A243:AK243"/>
-    <mergeCell ref="A237:AK237"/>
-    <mergeCell ref="A227:AK227"/>
     <mergeCell ref="A186:AK186"/>
     <mergeCell ref="A178:AK178"/>
-    <mergeCell ref="A169:AK169"/>
-    <mergeCell ref="A2:AK2"/>
-    <mergeCell ref="A60:AK60"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22263,7 +22296,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC28CD21-0D0B-4F46-BC27-107466C7A67F}">
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr defaultColWidth="17.125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.25" style="32" customWidth="1"/>
@@ -22892,7 +22925,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="40"/>
-      <c r="J18" s="51" t="s">
+      <c r="J18" s="45" t="s">
         <v>641</v>
       </c>
       <c r="K18" s="29">
@@ -22931,7 +22964,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="29"/>
-      <c r="J19" s="51" t="s">
+      <c r="J19" s="45" t="s">
         <v>642</v>
       </c>
       <c r="K19" s="29">
@@ -23100,7 +23133,7 @@
         <v>1</v>
       </c>
       <c r="N23" s="29">
-        <v>1110</v>
+        <v>1200</v>
       </c>
       <c r="O23" s="29" t="s">
         <v>422</v>
@@ -23139,111 +23172,111 @@
         <v>1</v>
       </c>
       <c r="N24" s="29">
-        <v>1120</v>
+        <v>1300</v>
       </c>
       <c r="O24" s="30" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A25" s="29">
+    <row r="25" spans="1:15" ht="14.25" x14ac:dyDescent="0.3">
+      <c r="A25" s="50">
+        <v>1400</v>
+      </c>
+      <c r="B25" s="50">
+        <v>10</v>
+      </c>
+      <c r="C25" s="50"/>
+      <c r="D25" s="50" t="s">
+        <v>744</v>
+      </c>
+      <c r="E25" s="50" t="s">
+        <v>745</v>
+      </c>
+      <c r="F25" s="50"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="50">
+        <v>0</v>
+      </c>
+      <c r="I25" s="51"/>
+      <c r="J25" s="52" t="s">
+        <v>743</v>
+      </c>
+      <c r="K25" s="50">
+        <v>1</v>
+      </c>
+      <c r="L25" s="50">
+        <v>0</v>
+      </c>
+      <c r="M25" s="50">
+        <v>1</v>
+      </c>
+      <c r="N25" s="50">
+        <v>1400</v>
+      </c>
+      <c r="O25" s="50" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="14.25" x14ac:dyDescent="0.3">
+      <c r="A26" s="50">
+        <v>1500</v>
+      </c>
+      <c r="B26" s="50">
+        <v>10</v>
+      </c>
+      <c r="C26" s="50"/>
+      <c r="D26" s="50" t="s">
+        <v>746</v>
+      </c>
+      <c r="E26" s="50" t="s">
+        <v>747</v>
+      </c>
+      <c r="F26" s="50"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="50">
+        <v>0</v>
+      </c>
+      <c r="I26" s="51"/>
+      <c r="J26" s="52" t="s">
+        <v>743</v>
+      </c>
+      <c r="K26" s="50">
+        <v>1</v>
+      </c>
+      <c r="L26" s="50">
+        <v>0</v>
+      </c>
+      <c r="M26" s="50">
+        <v>1</v>
+      </c>
+      <c r="N26" s="50">
+        <v>1500</v>
+      </c>
+      <c r="O26" s="50" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A27" s="29">
         <v>30</v>
       </c>
-      <c r="B25" s="29"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29" t="s">
-        <v>414</v>
-      </c>
-      <c r="E25" s="29" t="s">
-        <v>415</v>
-      </c>
-      <c r="F25" s="29"/>
-      <c r="G25" s="40" t="s">
-        <v>298</v>
-      </c>
-      <c r="H25" s="29">
-        <v>0</v>
-      </c>
-      <c r="I25" s="29"/>
-      <c r="J25" s="29"/>
-      <c r="K25" s="29">
-        <v>1</v>
-      </c>
-      <c r="L25" s="29">
-        <v>0</v>
-      </c>
-      <c r="M25" s="30">
-        <v>1</v>
-      </c>
-      <c r="N25" s="29">
-        <v>91</v>
-      </c>
-      <c r="O25" s="29" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A26" s="29">
-        <v>3010</v>
-      </c>
-      <c r="B26" s="29">
-        <v>30</v>
-      </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29" t="s">
-        <v>416</v>
-      </c>
-      <c r="E26" s="29" t="s">
-        <v>442</v>
-      </c>
-      <c r="F26" s="29"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="29">
-        <v>0</v>
-      </c>
-      <c r="I26" s="40"/>
-      <c r="J26" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="K26" s="29">
-        <v>1</v>
-      </c>
-      <c r="L26" s="29">
-        <v>0</v>
-      </c>
-      <c r="M26" s="30">
-        <v>1</v>
-      </c>
-      <c r="N26" s="29">
-        <v>9110</v>
-      </c>
-      <c r="O26" s="29" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A27" s="29">
-        <v>3020</v>
-      </c>
-      <c r="B27" s="29">
-        <v>30</v>
-      </c>
+      <c r="B27" s="29"/>
       <c r="C27" s="29"/>
       <c r="D27" s="29" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E27" s="29" t="s">
-        <v>443</v>
+        <v>415</v>
       </c>
       <c r="F27" s="29"/>
-      <c r="G27" s="40"/>
+      <c r="G27" s="40" t="s">
+        <v>298</v>
+      </c>
       <c r="H27" s="29">
         <v>0</v>
       </c>
-      <c r="I27" s="40"/>
-      <c r="J27" s="7" t="s">
-        <v>419</v>
-      </c>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
       <c r="K27" s="29">
         <v>1</v>
       </c>
@@ -23254,25 +23287,25 @@
         <v>1</v>
       </c>
       <c r="N27" s="29">
-        <v>9120</v>
+        <v>91</v>
       </c>
       <c r="O27" s="29" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A28" s="29">
-        <v>3030</v>
+        <v>3010</v>
       </c>
       <c r="B28" s="29">
         <v>30</v>
       </c>
       <c r="C28" s="29"/>
       <c r="D28" s="29" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E28" s="29" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F28" s="29"/>
       <c r="G28" s="40"/>
@@ -23280,8 +23313,8 @@
         <v>0</v>
       </c>
       <c r="I28" s="40"/>
-      <c r="J28" s="36" t="s">
-        <v>742</v>
+      <c r="J28" s="7" t="s">
+        <v>419</v>
       </c>
       <c r="K28" s="29">
         <v>1</v>
@@ -23293,9 +23326,87 @@
         <v>1</v>
       </c>
       <c r="N28" s="29">
+        <v>9110</v>
+      </c>
+      <c r="O28" s="29" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="14.25" x14ac:dyDescent="0.3">
+      <c r="A29" s="29">
+        <v>3020</v>
+      </c>
+      <c r="B29" s="29">
+        <v>30</v>
+      </c>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29" t="s">
+        <v>417</v>
+      </c>
+      <c r="E29" s="29" t="s">
+        <v>443</v>
+      </c>
+      <c r="F29" s="29"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="29">
+        <v>0</v>
+      </c>
+      <c r="I29" s="40"/>
+      <c r="J29" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="K29" s="29">
+        <v>1</v>
+      </c>
+      <c r="L29" s="29">
+        <v>0</v>
+      </c>
+      <c r="M29" s="30">
+        <v>1</v>
+      </c>
+      <c r="N29" s="29">
+        <v>9120</v>
+      </c>
+      <c r="O29" s="29" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A30" s="29">
+        <v>3030</v>
+      </c>
+      <c r="B30" s="29">
+        <v>30</v>
+      </c>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29" t="s">
+        <v>418</v>
+      </c>
+      <c r="E30" s="29" t="s">
+        <v>444</v>
+      </c>
+      <c r="F30" s="29"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="29">
+        <v>0</v>
+      </c>
+      <c r="I30" s="40"/>
+      <c r="J30" s="36" t="s">
+        <v>742</v>
+      </c>
+      <c r="K30" s="29">
+        <v>1</v>
+      </c>
+      <c r="L30" s="29">
+        <v>0</v>
+      </c>
+      <c r="M30" s="30">
+        <v>1</v>
+      </c>
+      <c r="N30" s="29">
         <v>9130</v>
       </c>
-      <c r="O28" s="29" t="s">
+      <c r="O30" s="29" t="s">
         <v>421</v>
       </c>
     </row>
@@ -23408,30 +23519,30 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="47" t="s">
         <v>644</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="47" t="s">
         <v>643</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53" t="s">
+      <c r="C2" s="47"/>
+      <c r="D2" s="47" t="s">
         <v>647</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="E2" s="47" t="s">
         <v>629</v>
       </c>
-      <c r="F2" s="53" t="s">
+      <c r="F2" s="47" t="s">
         <v>567</v>
       </c>
-      <c r="G2" s="53" t="s">
+      <c r="G2" s="47" t="s">
         <v>568</v>
       </c>
-      <c r="H2" s="53" t="s">
+      <c r="H2" s="47" t="s">
         <v>648</v>
       </c>
-      <c r="I2" s="55"/>
-      <c r="J2" s="53" t="s">
+      <c r="I2" s="49"/>
+      <c r="J2" s="47" t="s">
         <v>649</v>
       </c>
     </row>
@@ -23439,43 +23550,43 @@
       <c r="A3" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="47" t="s">
         <v>656</v>
       </c>
-      <c r="C3" s="53"/>
+      <c r="C3" s="47"/>
       <c r="D3" s="26" t="s">
         <v>582</v>
       </c>
       <c r="E3" s="26" t="s">
         <v>655</v>
       </c>
-      <c r="F3" s="53" t="s">
+      <c r="F3" s="47" t="s">
         <v>568</v>
       </c>
-      <c r="G3" s="53" t="s">
+      <c r="G3" s="47" t="s">
         <v>567</v>
       </c>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53" t="s">
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47" t="s">
         <v>654</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="47" t="s">
         <v>657</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53" t="s">
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47" t="s">
         <v>659</v>
       </c>
-      <c r="J4" s="53" t="s">
+      <c r="J4" s="47" t="s">
         <v>658</v>
       </c>
     </row>

--- a/public/import_template/v0.2node/node_module.xlsx
+++ b/public/import_template/v0.2node/node_module.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\ddit\code\umi_max.260226_github\public\import_template\v0.2node\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18DC96FE-4A21-4321-B201-D19F6DB3822A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B01829-0163-4698-B963-6157DFBB3E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="762" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2342" uniqueCount="748">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2350" uniqueCount="752">
   <si>
     <t>字段中文名</t>
   </si>
@@ -2749,6 +2749,22 @@
   </si>
   <si>
     <t>/dynamicbs1/enh/cfgp/eg_m_mts_tssb</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>接口日志管理E</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统日志管理E</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>/dynamicbs1/enh/cfgp/m_sys_api_log</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>/dynamicbs1/enh/cfgp/m_sys_app_log</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3094,7 +3110,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3253,6 +3269,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -22270,6 +22289,7 @@
   </sheetData>
   <autoFilter ref="A1:AJ256" xr:uid="{0580B1DF-60C2-4E2B-940A-667729080FCF}"/>
   <mergeCells count="17">
+    <mergeCell ref="A178:AK178"/>
     <mergeCell ref="A169:AK169"/>
     <mergeCell ref="A2:AK2"/>
     <mergeCell ref="A60:AK60"/>
@@ -22286,7 +22306,6 @@
     <mergeCell ref="A208:AK208"/>
     <mergeCell ref="A201:AK201"/>
     <mergeCell ref="A186:AK186"/>
-    <mergeCell ref="A178:AK178"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22296,13 +22315,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC28CD21-0D0B-4F46-BC27-107466C7A67F}">
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr defaultColWidth="17.125" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.25" style="32" customWidth="1"/>
     <col min="2" max="2" width="9" style="32" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.5" style="32" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="32" customWidth="1"/>
+    <col min="4" max="4" width="12.125" style="32" customWidth="1"/>
     <col min="5" max="5" width="45.5" style="32" customWidth="1"/>
     <col min="6" max="6" width="10.5" style="32" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.875" style="32" bestFit="1" customWidth="1"/>
@@ -23256,105 +23275,105 @@
         <v>421</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="14.25" x14ac:dyDescent="0.25">
-      <c r="A27" s="29">
+    <row r="27" spans="1:15" ht="14.25" x14ac:dyDescent="0.3">
+      <c r="A27" s="50">
+        <v>1600</v>
+      </c>
+      <c r="B27" s="50">
+        <v>10</v>
+      </c>
+      <c r="C27" s="50"/>
+      <c r="D27" s="59" t="s">
+        <v>748</v>
+      </c>
+      <c r="E27" s="50" t="s">
+        <v>750</v>
+      </c>
+      <c r="F27" s="50"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="50">
+        <v>0</v>
+      </c>
+      <c r="I27" s="51"/>
+      <c r="J27" s="52" t="s">
+        <v>743</v>
+      </c>
+      <c r="K27" s="50">
+        <v>1</v>
+      </c>
+      <c r="L27" s="50">
+        <v>0</v>
+      </c>
+      <c r="M27" s="50">
+        <v>1</v>
+      </c>
+      <c r="N27" s="50">
+        <v>1600</v>
+      </c>
+      <c r="O27" s="50" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="14.25" x14ac:dyDescent="0.3">
+      <c r="A28" s="50">
+        <v>1700</v>
+      </c>
+      <c r="B28" s="50">
+        <v>10</v>
+      </c>
+      <c r="C28" s="50"/>
+      <c r="D28" s="59" t="s">
+        <v>749</v>
+      </c>
+      <c r="E28" s="50" t="s">
+        <v>751</v>
+      </c>
+      <c r="F28" s="50"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="50">
+        <v>0</v>
+      </c>
+      <c r="I28" s="51"/>
+      <c r="J28" s="52" t="s">
+        <v>743</v>
+      </c>
+      <c r="K28" s="50">
+        <v>1</v>
+      </c>
+      <c r="L28" s="50">
+        <v>0</v>
+      </c>
+      <c r="M28" s="50">
+        <v>1</v>
+      </c>
+      <c r="N28" s="50">
+        <v>1700</v>
+      </c>
+      <c r="O28" s="50" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A29" s="29">
         <v>30</v>
       </c>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29" t="s">
-        <v>414</v>
-      </c>
-      <c r="E27" s="29" t="s">
-        <v>415</v>
-      </c>
-      <c r="F27" s="29"/>
-      <c r="G27" s="40" t="s">
-        <v>298</v>
-      </c>
-      <c r="H27" s="29">
-        <v>0</v>
-      </c>
-      <c r="I27" s="29"/>
-      <c r="J27" s="29"/>
-      <c r="K27" s="29">
-        <v>1</v>
-      </c>
-      <c r="L27" s="29">
-        <v>0</v>
-      </c>
-      <c r="M27" s="30">
-        <v>1</v>
-      </c>
-      <c r="N27" s="29">
-        <v>91</v>
-      </c>
-      <c r="O27" s="29" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A28" s="29">
-        <v>3010</v>
-      </c>
-      <c r="B28" s="29">
-        <v>30</v>
-      </c>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29" t="s">
-        <v>416</v>
-      </c>
-      <c r="E28" s="29" t="s">
-        <v>442</v>
-      </c>
-      <c r="F28" s="29"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="29">
-        <v>0</v>
-      </c>
-      <c r="I28" s="40"/>
-      <c r="J28" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="K28" s="29">
-        <v>1</v>
-      </c>
-      <c r="L28" s="29">
-        <v>0</v>
-      </c>
-      <c r="M28" s="30">
-        <v>1</v>
-      </c>
-      <c r="N28" s="29">
-        <v>9110</v>
-      </c>
-      <c r="O28" s="29" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" ht="14.25" x14ac:dyDescent="0.3">
-      <c r="A29" s="29">
-        <v>3020</v>
-      </c>
-      <c r="B29" s="29">
-        <v>30</v>
-      </c>
+      <c r="B29" s="29"/>
       <c r="C29" s="29"/>
       <c r="D29" s="29" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E29" s="29" t="s">
-        <v>443</v>
+        <v>415</v>
       </c>
       <c r="F29" s="29"/>
-      <c r="G29" s="40"/>
+      <c r="G29" s="40" t="s">
+        <v>298</v>
+      </c>
       <c r="H29" s="29">
         <v>0</v>
       </c>
-      <c r="I29" s="40"/>
-      <c r="J29" s="7" t="s">
-        <v>419</v>
-      </c>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
       <c r="K29" s="29">
         <v>1</v>
       </c>
@@ -23365,25 +23384,25 @@
         <v>1</v>
       </c>
       <c r="N29" s="29">
-        <v>9120</v>
+        <v>91</v>
       </c>
       <c r="O29" s="29" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A30" s="29">
-        <v>3030</v>
+        <v>3010</v>
       </c>
       <c r="B30" s="29">
         <v>30</v>
       </c>
       <c r="C30" s="29"/>
       <c r="D30" s="29" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E30" s="29" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F30" s="29"/>
       <c r="G30" s="40"/>
@@ -23391,8 +23410,8 @@
         <v>0</v>
       </c>
       <c r="I30" s="40"/>
-      <c r="J30" s="36" t="s">
-        <v>742</v>
+      <c r="J30" s="7" t="s">
+        <v>419</v>
       </c>
       <c r="K30" s="29">
         <v>1</v>
@@ -23404,9 +23423,87 @@
         <v>1</v>
       </c>
       <c r="N30" s="29">
+        <v>9110</v>
+      </c>
+      <c r="O30" s="29" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="14.25" x14ac:dyDescent="0.3">
+      <c r="A31" s="29">
+        <v>3020</v>
+      </c>
+      <c r="B31" s="29">
+        <v>30</v>
+      </c>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29" t="s">
+        <v>417</v>
+      </c>
+      <c r="E31" s="29" t="s">
+        <v>443</v>
+      </c>
+      <c r="F31" s="29"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="29">
+        <v>0</v>
+      </c>
+      <c r="I31" s="40"/>
+      <c r="J31" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="K31" s="29">
+        <v>1</v>
+      </c>
+      <c r="L31" s="29">
+        <v>0</v>
+      </c>
+      <c r="M31" s="30">
+        <v>1</v>
+      </c>
+      <c r="N31" s="29">
+        <v>9120</v>
+      </c>
+      <c r="O31" s="29" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A32" s="29">
+        <v>3030</v>
+      </c>
+      <c r="B32" s="29">
+        <v>30</v>
+      </c>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29" t="s">
+        <v>418</v>
+      </c>
+      <c r="E32" s="29" t="s">
+        <v>444</v>
+      </c>
+      <c r="F32" s="29"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="29">
+        <v>0</v>
+      </c>
+      <c r="I32" s="40"/>
+      <c r="J32" s="36" t="s">
+        <v>742</v>
+      </c>
+      <c r="K32" s="29">
+        <v>1</v>
+      </c>
+      <c r="L32" s="29">
+        <v>0</v>
+      </c>
+      <c r="M32" s="30">
+        <v>1</v>
+      </c>
+      <c r="N32" s="29">
         <v>9130</v>
       </c>
-      <c r="O30" s="29" t="s">
+      <c r="O32" s="29" t="s">
         <v>421</v>
       </c>
     </row>
